--- a/jnciesproadmap/JNCIE-SP_Juniper_SP_Engineer_Lab_Roadmap.xlsx
+++ b/jnciesproadmap/JNCIE-SP_Juniper_SP_Engineer_Lab_Roadmap.xlsx
@@ -201,16 +201,16 @@
     <t xml:space="preserve">Filter, match, count, display detail/extensive, monitor, request support information and save evidence efficiently.</t>
   </si>
   <si>
+    <t>LAB-004</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Routing tables and next-hop resolution</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Trace a route across inet.0, inet.3, mpls.0 and protocol-specific tables including hidden routes.</t>
+  </si>
+  <si>
     <t xml:space="preserve">☐ Not Started</t>
-  </si>
-  <si>
-    <t>LAB-004</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Routing tables and next-hop resolution</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Trace a route across inet.0, inet.3, mpls.0 and protocol-specific tables including hidden routes.</t>
   </si>
   <si>
     <t>LAB-005</t>
@@ -2686,7 +2686,7 @@
       </c>
       <c r="B6" s="8">
         <f>COUNTIF('Lab Checklist'!$L$2:$L$124,"*Completed*")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="7">
@@ -2700,11 +2700,11 @@
       <c r="F6" s="9"/>
       <c r="G6" s="10">
         <f>IFERROR(B6/A6,0)</f>
-        <v>0.016260162601626018</v>
+        <v>0.024390243902439025</v>
       </c>
       <c r="H6" s="8">
         <f>SUMIF('Lab Checklist'!$L$2:$L$124,"*Completed*",'Lab Checklist'!$H$2:$H$124)</f>
-        <v>4</v>
+        <v>6</v>
       </c>
     </row>
     <row r="8" ht="15">
@@ -2735,11 +2735,11 @@
       </c>
       <c r="C9" s="16">
         <f>COUNTIFS('Lab Checklist'!$B$2:$B$124,A9,'Lab Checklist'!$L$2:$L$124,"*Completed*")</f>
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="D9" s="17">
         <f>IFERROR(C9/B9,0)</f>
-        <v>0.20000000000000001</v>
+        <v>0.29999999999999999</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>13</v>
@@ -2956,7 +2956,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2" id="{2F82F829-2141-4B30-A417-98EBA9B532D7}">
+          <x14:cfRule type="dataBar" priority="2" id="{F3328177-44D9-473A-BA9E-58720EA418BB}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3181,7 +3181,7 @@
         <v>51</v>
       </c>
       <c r="L4" s="23" t="s">
-        <v>57</v>
+        <v>49</v>
       </c>
       <c r="M4" s="23">
         <v>0</v>
@@ -3195,7 +3195,7 @@
     </row>
     <row r="5" ht="38.25">
       <c r="A5" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="B5" s="23" t="s">
         <v>12</v>
@@ -3207,10 +3207,10 @@
         <v>43</v>
       </c>
       <c r="E5" s="23" t="s">
+        <v>58</v>
+      </c>
+      <c r="F5" s="24" t="s">
         <v>59</v>
-      </c>
-      <c r="F5" s="24" t="s">
-        <v>60</v>
       </c>
       <c r="G5" s="24" t="s">
         <v>46</v>
@@ -3228,7 +3228,7 @@
         <v>54</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M5" s="23">
         <v>0</v>
@@ -3272,10 +3272,10 @@
         <v>48</v>
       </c>
       <c r="K6" s="23" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M6" s="23">
         <v>0</v>
@@ -3322,7 +3322,7 @@
         <v>61</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M7" s="23">
         <v>0</v>
@@ -3369,7 +3369,7 @@
         <v>64</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M8" s="23">
         <v>0</v>
@@ -3416,7 +3416,7 @@
         <v>67</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M9" s="23">
         <v>0</v>
@@ -3463,7 +3463,7 @@
         <v>70</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M10" s="23">
         <v>0</v>
@@ -3510,7 +3510,7 @@
         <v>73</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M11" s="23">
         <v>0</v>
@@ -3555,7 +3555,7 @@
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M12" s="23">
         <v>0</v>
@@ -3602,7 +3602,7 @@
         <v>79</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M13" s="23">
         <v>0</v>
@@ -3649,7 +3649,7 @@
         <v>84</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M14" s="23">
         <v>0</v>
@@ -3696,7 +3696,7 @@
         <v>87</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M15" s="23">
         <v>0</v>
@@ -3743,7 +3743,7 @@
         <v>90</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M16" s="23">
         <v>0</v>
@@ -3790,7 +3790,7 @@
         <v>93</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M17" s="23">
         <v>0</v>
@@ -3837,7 +3837,7 @@
         <v>96</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M18" s="23">
         <v>0</v>
@@ -3884,7 +3884,7 @@
         <v>99</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M19" s="23">
         <v>0</v>
@@ -3931,7 +3931,7 @@
         <v>102</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M20" s="23">
         <v>0</v>
@@ -3978,7 +3978,7 @@
         <v>105</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M21" s="23">
         <v>0</v>
@@ -4025,7 +4025,7 @@
         <v>108</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M22" s="23">
         <v>0</v>
@@ -4072,7 +4072,7 @@
         <v>111</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M23" s="23">
         <v>0</v>
@@ -4117,7 +4117,7 @@
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M24" s="23">
         <v>0</v>
@@ -4164,7 +4164,7 @@
         <v>117</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M25" s="23">
         <v>0</v>
@@ -4211,7 +4211,7 @@
         <v>121</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M26" s="23">
         <v>0</v>
@@ -4258,7 +4258,7 @@
         <v>124</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M27" s="23">
         <v>0</v>
@@ -4305,7 +4305,7 @@
         <v>127</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M28" s="23">
         <v>0</v>
@@ -4352,7 +4352,7 @@
         <v>130</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M29" s="23">
         <v>0</v>
@@ -4399,7 +4399,7 @@
         <v>133</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M30" s="23">
         <v>0</v>
@@ -4446,7 +4446,7 @@
         <v>136</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M31" s="23">
         <v>0</v>
@@ -4493,7 +4493,7 @@
         <v>139</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M32" s="23">
         <v>0</v>
@@ -4540,7 +4540,7 @@
         <v>142</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M33" s="23">
         <v>0</v>
@@ -4587,7 +4587,7 @@
         <v>145</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M34" s="23">
         <v>0</v>
@@ -4634,7 +4634,7 @@
         <v>148</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M35" s="23">
         <v>0</v>
@@ -4679,7 +4679,7 @@
       </c>
       <c r="K36" s="23"/>
       <c r="L36" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M36" s="23">
         <v>0</v>
@@ -4726,7 +4726,7 @@
         <v>154</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M37" s="23">
         <v>0</v>
@@ -4773,7 +4773,7 @@
         <v>159</v>
       </c>
       <c r="L38" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M38" s="23">
         <v>0</v>
@@ -4820,7 +4820,7 @@
         <v>162</v>
       </c>
       <c r="L39" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M39" s="23">
         <v>0</v>
@@ -4867,7 +4867,7 @@
         <v>165</v>
       </c>
       <c r="L40" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M40" s="23">
         <v>0</v>
@@ -4914,7 +4914,7 @@
         <v>168</v>
       </c>
       <c r="L41" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M41" s="23">
         <v>0</v>
@@ -4961,7 +4961,7 @@
         <v>171</v>
       </c>
       <c r="L42" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M42" s="23">
         <v>0</v>
@@ -5008,7 +5008,7 @@
         <v>174</v>
       </c>
       <c r="L43" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M43" s="23">
         <v>0</v>
@@ -5055,7 +5055,7 @@
         <v>177</v>
       </c>
       <c r="L44" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M44" s="23">
         <v>0</v>
@@ -5102,7 +5102,7 @@
         <v>180</v>
       </c>
       <c r="L45" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M45" s="23">
         <v>0</v>
@@ -5149,7 +5149,7 @@
         <v>183</v>
       </c>
       <c r="L46" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M46" s="23">
         <v>0</v>
@@ -5196,7 +5196,7 @@
         <v>186</v>
       </c>
       <c r="L47" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M47" s="23">
         <v>0</v>
@@ -5243,7 +5243,7 @@
         <v>189</v>
       </c>
       <c r="L48" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M48" s="23">
         <v>0</v>
@@ -5290,7 +5290,7 @@
         <v>192</v>
       </c>
       <c r="L49" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M49" s="23">
         <v>0</v>
@@ -5335,7 +5335,7 @@
       </c>
       <c r="K50" s="23"/>
       <c r="L50" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M50" s="23">
         <v>0</v>
@@ -5382,7 +5382,7 @@
         <v>198</v>
       </c>
       <c r="L51" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M51" s="23">
         <v>0</v>
@@ -5429,7 +5429,7 @@
         <v>204</v>
       </c>
       <c r="L52" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M52" s="23">
         <v>0</v>
@@ -5476,7 +5476,7 @@
         <v>207</v>
       </c>
       <c r="L53" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M53" s="23">
         <v>0</v>
@@ -5523,7 +5523,7 @@
         <v>210</v>
       </c>
       <c r="L54" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M54" s="23">
         <v>0</v>
@@ -5570,7 +5570,7 @@
         <v>213</v>
       </c>
       <c r="L55" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M55" s="23">
         <v>0</v>
@@ -5617,7 +5617,7 @@
         <v>216</v>
       </c>
       <c r="L56" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M56" s="23">
         <v>0</v>
@@ -5664,7 +5664,7 @@
         <v>219</v>
       </c>
       <c r="L57" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M57" s="23">
         <v>0</v>
@@ -5709,7 +5709,7 @@
       </c>
       <c r="K58" s="23"/>
       <c r="L58" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M58" s="23">
         <v>0</v>
@@ -5756,7 +5756,7 @@
         <v>225</v>
       </c>
       <c r="L59" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M59" s="23">
         <v>0</v>
@@ -5803,7 +5803,7 @@
         <v>229</v>
       </c>
       <c r="L60" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M60" s="23">
         <v>0</v>
@@ -5850,7 +5850,7 @@
         <v>232</v>
       </c>
       <c r="L61" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M61" s="23">
         <v>0</v>
@@ -5897,7 +5897,7 @@
         <v>235</v>
       </c>
       <c r="L62" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M62" s="23">
         <v>0</v>
@@ -5944,7 +5944,7 @@
         <v>238</v>
       </c>
       <c r="L63" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M63" s="23">
         <v>0</v>
@@ -5991,7 +5991,7 @@
         <v>241</v>
       </c>
       <c r="L64" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M64" s="23">
         <v>0</v>
@@ -6038,7 +6038,7 @@
         <v>244</v>
       </c>
       <c r="L65" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M65" s="23">
         <v>0</v>
@@ -6085,7 +6085,7 @@
         <v>247</v>
       </c>
       <c r="L66" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M66" s="23">
         <v>0</v>
@@ -6132,7 +6132,7 @@
         <v>250</v>
       </c>
       <c r="L67" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M67" s="23">
         <v>0</v>
@@ -6179,7 +6179,7 @@
         <v>253</v>
       </c>
       <c r="L68" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M68" s="23">
         <v>0</v>
@@ -6226,7 +6226,7 @@
         <v>256</v>
       </c>
       <c r="L69" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M69" s="23">
         <v>0</v>
@@ -6271,7 +6271,7 @@
       </c>
       <c r="K70" s="23"/>
       <c r="L70" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M70" s="23">
         <v>0</v>
@@ -6318,7 +6318,7 @@
         <v>262</v>
       </c>
       <c r="L71" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M71" s="23">
         <v>0</v>
@@ -6365,7 +6365,7 @@
         <v>266</v>
       </c>
       <c r="L72" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M72" s="23">
         <v>0</v>
@@ -6412,7 +6412,7 @@
         <v>269</v>
       </c>
       <c r="L73" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M73" s="23">
         <v>0</v>
@@ -6459,7 +6459,7 @@
         <v>272</v>
       </c>
       <c r="L74" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M74" s="23">
         <v>0</v>
@@ -6506,7 +6506,7 @@
         <v>275</v>
       </c>
       <c r="L75" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M75" s="23">
         <v>0</v>
@@ -6553,7 +6553,7 @@
         <v>278</v>
       </c>
       <c r="L76" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M76" s="23">
         <v>0</v>
@@ -6600,7 +6600,7 @@
         <v>281</v>
       </c>
       <c r="L77" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M77" s="23">
         <v>0</v>
@@ -6647,7 +6647,7 @@
         <v>284</v>
       </c>
       <c r="L78" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M78" s="23">
         <v>0</v>
@@ -6692,7 +6692,7 @@
       </c>
       <c r="K79" s="23"/>
       <c r="L79" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M79" s="23">
         <v>0</v>
@@ -6739,7 +6739,7 @@
         <v>290</v>
       </c>
       <c r="L80" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M80" s="23">
         <v>0</v>
@@ -6786,7 +6786,7 @@
         <v>294</v>
       </c>
       <c r="L81" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M81" s="23">
         <v>0</v>
@@ -6833,7 +6833,7 @@
         <v>297</v>
       </c>
       <c r="L82" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M82" s="23">
         <v>0</v>
@@ -6880,7 +6880,7 @@
         <v>300</v>
       </c>
       <c r="L83" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M83" s="23">
         <v>0</v>
@@ -6927,7 +6927,7 @@
         <v>303</v>
       </c>
       <c r="L84" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M84" s="23">
         <v>0</v>
@@ -6974,7 +6974,7 @@
         <v>306</v>
       </c>
       <c r="L85" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M85" s="23">
         <v>0</v>
@@ -7021,7 +7021,7 @@
         <v>309</v>
       </c>
       <c r="L86" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M86" s="23">
         <v>0</v>
@@ -7068,7 +7068,7 @@
         <v>312</v>
       </c>
       <c r="L87" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M87" s="23">
         <v>0</v>
@@ -7115,7 +7115,7 @@
         <v>315</v>
       </c>
       <c r="L88" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M88" s="23">
         <v>0</v>
@@ -7160,7 +7160,7 @@
       </c>
       <c r="K89" s="23"/>
       <c r="L89" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M89" s="23">
         <v>0</v>
@@ -7207,7 +7207,7 @@
         <v>321</v>
       </c>
       <c r="L90" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M90" s="23">
         <v>0</v>
@@ -7254,7 +7254,7 @@
         <v>325</v>
       </c>
       <c r="L91" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M91" s="23">
         <v>0</v>
@@ -7301,7 +7301,7 @@
         <v>328</v>
       </c>
       <c r="L92" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M92" s="23">
         <v>0</v>
@@ -7348,7 +7348,7 @@
         <v>331</v>
       </c>
       <c r="L93" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M93" s="23">
         <v>0</v>
@@ -7395,7 +7395,7 @@
         <v>334</v>
       </c>
       <c r="L94" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M94" s="23">
         <v>0</v>
@@ -7442,7 +7442,7 @@
         <v>337</v>
       </c>
       <c r="L95" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M95" s="23">
         <v>0</v>
@@ -7489,7 +7489,7 @@
         <v>340</v>
       </c>
       <c r="L96" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M96" s="23">
         <v>0</v>
@@ -7536,7 +7536,7 @@
         <v>343</v>
       </c>
       <c r="L97" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M97" s="23">
         <v>0</v>
@@ -7581,7 +7581,7 @@
       </c>
       <c r="K98" s="23"/>
       <c r="L98" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M98" s="23">
         <v>0</v>
@@ -7628,7 +7628,7 @@
         <v>349</v>
       </c>
       <c r="L99" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M99" s="23">
         <v>0</v>
@@ -7675,7 +7675,7 @@
         <v>353</v>
       </c>
       <c r="L100" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M100" s="23">
         <v>0</v>
@@ -7722,7 +7722,7 @@
         <v>356</v>
       </c>
       <c r="L101" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M101" s="23">
         <v>0</v>
@@ -7769,7 +7769,7 @@
         <v>359</v>
       </c>
       <c r="L102" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M102" s="23">
         <v>0</v>
@@ -7816,7 +7816,7 @@
         <v>362</v>
       </c>
       <c r="L103" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M103" s="23">
         <v>0</v>
@@ -7863,7 +7863,7 @@
         <v>365</v>
       </c>
       <c r="L104" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M104" s="23">
         <v>0</v>
@@ -7908,7 +7908,7 @@
       </c>
       <c r="K105" s="23"/>
       <c r="L105" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M105" s="23">
         <v>0</v>
@@ -7955,7 +7955,7 @@
         <v>371</v>
       </c>
       <c r="L106" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M106" s="23">
         <v>0</v>
@@ -8002,7 +8002,7 @@
         <v>376</v>
       </c>
       <c r="L107" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M107" s="23">
         <v>0</v>
@@ -8049,7 +8049,7 @@
         <v>379</v>
       </c>
       <c r="L108" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M108" s="23">
         <v>0</v>
@@ -8096,7 +8096,7 @@
         <v>382</v>
       </c>
       <c r="L109" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M109" s="23">
         <v>0</v>
@@ -8143,7 +8143,7 @@
         <v>385</v>
       </c>
       <c r="L110" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M110" s="23">
         <v>0</v>
@@ -8190,7 +8190,7 @@
         <v>388</v>
       </c>
       <c r="L111" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M111" s="23">
         <v>0</v>
@@ -8237,7 +8237,7 @@
         <v>391</v>
       </c>
       <c r="L112" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M112" s="23">
         <v>0</v>
@@ -8284,7 +8284,7 @@
         <v>394</v>
       </c>
       <c r="L113" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M113" s="23">
         <v>0</v>
@@ -8331,7 +8331,7 @@
         <v>397</v>
       </c>
       <c r="L114" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M114" s="23">
         <v>0</v>
@@ -8376,7 +8376,7 @@
       </c>
       <c r="K115" s="23"/>
       <c r="L115" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M115" s="23">
         <v>0</v>
@@ -8423,7 +8423,7 @@
         <v>403</v>
       </c>
       <c r="L116" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M116" s="23">
         <v>0</v>
@@ -8470,7 +8470,7 @@
         <v>408</v>
       </c>
       <c r="L117" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M117" s="23">
         <v>0</v>
@@ -8517,7 +8517,7 @@
         <v>411</v>
       </c>
       <c r="L118" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M118" s="23">
         <v>0</v>
@@ -8564,7 +8564,7 @@
         <v>414</v>
       </c>
       <c r="L119" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M119" s="23">
         <v>0</v>
@@ -8611,7 +8611,7 @@
         <v>417</v>
       </c>
       <c r="L120" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M120" s="23">
         <v>0</v>
@@ -8658,7 +8658,7 @@
         <v>420</v>
       </c>
       <c r="L121" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M121" s="23">
         <v>0</v>
@@ -8705,7 +8705,7 @@
         <v>423</v>
       </c>
       <c r="L122" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M122" s="23">
         <v>0</v>
@@ -8752,7 +8752,7 @@
         <v>426</v>
       </c>
       <c r="L123" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M123" s="23">
         <v>0</v>
@@ -8799,7 +8799,7 @@
         <v>429</v>
       </c>
       <c r="L124" s="23" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="M124" s="23">
         <v>0</v>
@@ -8823,7 +8823,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" aboveAverage="0" operator="containsText" rank="0" text="Completed" id="{0D6ACE5B-3544-465C-B7CE-6B91FAE6D1CA}">
+          <x14:cfRule type="containsText" priority="2" aboveAverage="0" operator="containsText" rank="0" text="Completed" id="{9900F14E-E88E-4678-B37F-D2B18A80BDCB}">
             <xm:f>NOT(ISERROR(SEARCH("Completed",L2)))</xm:f>
             <x14:dxf>
               <font>
@@ -8841,7 +8841,7 @@
           <xm:sqref>L2:L124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" aboveAverage="0" operator="containsText" rank="0" text="In Progress" id="{E5A2633F-FE6D-4336-8F75-DF11F90DC9F4}">
+          <x14:cfRule type="containsText" priority="3" aboveAverage="0" operator="containsText" rank="0" text="In Progress" id="{328A7771-2D67-4AF9-927B-F5168AEDC497}">
             <xm:f>NOT(ISERROR(SEARCH("In Progress",L2)))</xm:f>
             <x14:dxf>
               <font>
@@ -8858,7 +8858,7 @@
           <xm:sqref>L2:L124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" aboveAverage="0" operator="containsText" rank="0" text="Revisit" id="{BA4E5BAD-3963-45B8-9C04-D3BD81E29477}">
+          <x14:cfRule type="containsText" priority="4" aboveAverage="0" operator="containsText" rank="0" text="Revisit" id="{D95E3601-8BBD-4AC2-8690-F9252B36512B}">
             <xm:f>NOT(ISERROR(SEARCH("Revisit",L2)))</xm:f>
             <x14:dxf>
               <font>
@@ -8875,7 +8875,7 @@
           <xm:sqref>L2:L124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="5" id="{D1B9B614-D747-4940-A57B-ECD921C404F4}">
+          <x14:cfRule type="dataBar" priority="5" id="{6FE29B43-BA9E-4E25-B324-55E9B9B9FD66}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8890,7 +8890,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{420FDE69-CEC2-44A1-AC4F-E2D53512F67D}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{776AAC6B-FEEC-4395-82D3-88E03D01DF9B}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"☐ Not Started,◐ In Progress,☑ Completed,↻ Revisit"</xm:f>
           </x14:formula1>
@@ -8899,7 +8899,7 @@
           </x14:formula2>
           <xm:sqref>L2:L124</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{96B9E689-C74A-45FE-96CE-2D9FC222556C}" type="whole" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{60F40BE6-F493-4A59-A361-5A88D59FABA0}" type="whole" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>
@@ -9545,7 +9545,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{7C177C08-5769-42A1-8B49-358F5827E7E3}" type="decimal" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{A308CF30-536E-4B1F-BF91-43B0354036A4}" type="decimal" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>
@@ -11016,7 +11016,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{D2A246AA-4F16-4E26-9D2B-D6FE2163F839}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{F5A6C0CF-EF64-4011-B35E-E0B3B77D0133}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Build,Troubleshoot,Rebuild,Timed Mock,Review"</xm:f>
           </x14:formula1>
@@ -11025,7 +11025,7 @@
           </x14:formula2>
           <xm:sqref>D2:D201</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{382C417B-8BC6-444A-BFEE-589C864C44C7}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{621BD406-F3F6-4FCF-BECB-8C0F543E05DD}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Pass,Partial,Fail"</xm:f>
           </x14:formula1>
@@ -11304,7 +11304,7 @@
     </row>
     <row r="2" ht="15">
       <c r="A2" s="1" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>

--- a/jnciesproadmap/JNCIE-SP_Juniper_SP_Engineer_Lab_Roadmap.xlsx
+++ b/jnciesproadmap/JNCIE-SP_Juniper_SP_Engineer_Lab_Roadmap.xlsx
@@ -210,16 +210,16 @@
     <t xml:space="preserve">Trace a route across inet.0, inet.3, mpls.0 and protocol-specific tables including hidden routes.</t>
   </si>
   <si>
+    <t>LAB-005</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Policy language fundamentals</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Build deterministic term-based import/export policies using prefix lists, communities and subroutines.</t>
+  </si>
+  <si>
     <t xml:space="preserve">☐ Not Started</t>
-  </si>
-  <si>
-    <t>LAB-005</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Policy language fundamentals</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Build deterministic term-based import/export policies using prefix lists, communities and subroutines.</t>
   </si>
   <si>
     <t>LAB-006</t>
@@ -1936,7 +1936,7 @@
       <protection hidden="0" locked="1"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="33">
+  <cellXfs count="35">
     <xf fontId="0" fillId="0" borderId="0" numFmtId="0" xfId="0" applyProtection="0">
       <protection hidden="0" locked="1"/>
     </xf>
@@ -2018,14 +2018,22 @@
       <alignment vertical="center" wrapText="1"/>
       <protection hidden="0" locked="1"/>
     </xf>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection hidden="0" locked="1"/>
+    </xf>
     <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="6" applyFont="1" applyProtection="1">
+      <protection hidden="0" locked="1"/>
+    </xf>
+    <xf fontId="8" fillId="0" borderId="0" numFmtId="164" xfId="6" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="8" fillId="0" borderId="0" numFmtId="0" xfId="6" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment wrapText="1"/>
-      <protection hidden="0" locked="1"/>
-    </xf>
-    <xf fontId="8" fillId="0" borderId="0" numFmtId="164" xfId="6" applyNumberFormat="1" applyFont="1" applyProtection="1">
       <protection hidden="0" locked="1"/>
     </xf>
     <xf fontId="9" fillId="2" borderId="0" numFmtId="0" xfId="6" applyFont="1" applyFill="1" applyProtection="1">
@@ -2686,7 +2694,7 @@
       </c>
       <c r="B6" s="8">
         <f>COUNTIF('Lab Checklist'!$L$2:$L$124,"*Completed*")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="C6" s="9"/>
       <c r="D6" s="7">
@@ -2700,11 +2708,11 @@
       <c r="F6" s="9"/>
       <c r="G6" s="10">
         <f>IFERROR(B6/A6,0)</f>
-        <v>0.024390243902439025</v>
+        <v>0.032520325203252036</v>
       </c>
       <c r="H6" s="8">
         <f>SUMIF('Lab Checklist'!$L$2:$L$124,"*Completed*",'Lab Checklist'!$H$2:$H$124)</f>
-        <v>6</v>
+        <v>8</v>
       </c>
     </row>
     <row r="8" ht="15">
@@ -2735,11 +2743,11 @@
       </c>
       <c r="C9" s="16">
         <f>COUNTIFS('Lab Checklist'!$B$2:$B$124,A9,'Lab Checklist'!$L$2:$L$124,"*Completed*")</f>
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="D9" s="17">
         <f>IFERROR(C9/B9,0)</f>
-        <v>0.29999999999999999</v>
+        <v>0.40000000000000002</v>
       </c>
       <c r="F9" s="18" t="s">
         <v>13</v>
@@ -2956,7 +2964,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="2" id="{F3328177-44D9-473A-BA9E-58720EA418BB}">
+          <x14:cfRule type="dataBar" priority="2" id="{0AC22710-0944-4EB7-ADE5-5186747B6EC5}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -3090,14 +3098,14 @@
       <c r="M2" s="23">
         <v>0</v>
       </c>
-      <c r="N2" s="23"/>
-      <c r="O2" s="25">
+      <c r="N2" s="25"/>
+      <c r="O2" s="26">
         <v>46243</v>
       </c>
-      <c r="P2" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q2" s="24"/>
+      <c r="P2" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q2" s="27"/>
     </row>
     <row r="3" ht="38.25">
       <c r="A3" s="23" t="s">
@@ -3139,12 +3147,12 @@
       <c r="M3" s="23">
         <v>0</v>
       </c>
-      <c r="N3" s="23"/>
-      <c r="O3" s="25"/>
-      <c r="P3" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q3" s="24"/>
+      <c r="N3" s="25"/>
+      <c r="O3" s="26"/>
+      <c r="P3" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q3" s="27"/>
     </row>
     <row r="4" ht="38.25">
       <c r="A4" s="23" t="s">
@@ -3186,12 +3194,12 @@
       <c r="M4" s="23">
         <v>0</v>
       </c>
-      <c r="N4" s="23"/>
-      <c r="O4" s="25"/>
-      <c r="P4" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q4" s="24"/>
+      <c r="N4" s="25"/>
+      <c r="O4" s="26"/>
+      <c r="P4" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q4" s="27"/>
     </row>
     <row r="5" ht="38.25">
       <c r="A5" s="23" t="s">
@@ -3228,21 +3236,21 @@
         <v>54</v>
       </c>
       <c r="L5" s="23" t="s">
-        <v>60</v>
+        <v>49</v>
       </c>
       <c r="M5" s="23">
         <v>0</v>
       </c>
-      <c r="N5" s="23"/>
-      <c r="O5" s="25"/>
-      <c r="P5" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q5" s="24"/>
+      <c r="N5" s="25"/>
+      <c r="O5" s="26"/>
+      <c r="P5" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q5" s="27"/>
     </row>
     <row r="6" ht="38.25">
       <c r="A6" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="B6" s="23" t="s">
         <v>12</v>
@@ -3254,10 +3262,10 @@
         <v>43</v>
       </c>
       <c r="E6" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="F6" s="24" t="s">
         <v>62</v>
-      </c>
-      <c r="F6" s="24" t="s">
-        <v>63</v>
       </c>
       <c r="G6" s="24" t="s">
         <v>46</v>
@@ -3275,17 +3283,17 @@
         <v>57</v>
       </c>
       <c r="L6" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M6" s="23">
         <v>0</v>
       </c>
-      <c r="N6" s="23"/>
-      <c r="O6" s="25"/>
-      <c r="P6" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q6" s="24"/>
+      <c r="N6" s="25"/>
+      <c r="O6" s="26"/>
+      <c r="P6" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q6" s="27"/>
     </row>
     <row r="7" ht="38.25">
       <c r="A7" s="23" t="s">
@@ -3319,20 +3327,20 @@
         <v>48</v>
       </c>
       <c r="K7" s="23" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="L7" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M7" s="23">
         <v>0</v>
       </c>
-      <c r="N7" s="23"/>
-      <c r="O7" s="25"/>
-      <c r="P7" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q7" s="24"/>
+      <c r="N7" s="25"/>
+      <c r="O7" s="26"/>
+      <c r="P7" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q7" s="27"/>
     </row>
     <row r="8" ht="38.25">
       <c r="A8" s="23" t="s">
@@ -3369,17 +3377,17 @@
         <v>64</v>
       </c>
       <c r="L8" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M8" s="23">
         <v>0</v>
       </c>
-      <c r="N8" s="23"/>
-      <c r="O8" s="25"/>
-      <c r="P8" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q8" s="24"/>
+      <c r="N8" s="25"/>
+      <c r="O8" s="26"/>
+      <c r="P8" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q8" s="27"/>
     </row>
     <row r="9" ht="38.25">
       <c r="A9" s="23" t="s">
@@ -3416,17 +3424,17 @@
         <v>67</v>
       </c>
       <c r="L9" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M9" s="23">
         <v>0</v>
       </c>
-      <c r="N9" s="23"/>
-      <c r="O9" s="25"/>
-      <c r="P9" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="24"/>
+      <c r="N9" s="25"/>
+      <c r="O9" s="26"/>
+      <c r="P9" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q9" s="27"/>
     </row>
     <row r="10" ht="38.25">
       <c r="A10" s="23" t="s">
@@ -3463,17 +3471,17 @@
         <v>70</v>
       </c>
       <c r="L10" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M10" s="23">
         <v>0</v>
       </c>
-      <c r="N10" s="23"/>
-      <c r="O10" s="25"/>
-      <c r="P10" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q10" s="24"/>
+      <c r="N10" s="25"/>
+      <c r="O10" s="26"/>
+      <c r="P10" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q10" s="27"/>
     </row>
     <row r="11" ht="38.25">
       <c r="A11" s="23" t="s">
@@ -3510,17 +3518,17 @@
         <v>73</v>
       </c>
       <c r="L11" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M11" s="23">
         <v>0</v>
       </c>
-      <c r="N11" s="23"/>
-      <c r="O11" s="25"/>
-      <c r="P11" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q11" s="24"/>
+      <c r="N11" s="25"/>
+      <c r="O11" s="26"/>
+      <c r="P11" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q11" s="27"/>
     </row>
     <row r="12" ht="38.25">
       <c r="A12" s="23" t="s">
@@ -3555,17 +3563,17 @@
       </c>
       <c r="K12" s="23"/>
       <c r="L12" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M12" s="23">
         <v>0</v>
       </c>
-      <c r="N12" s="23"/>
-      <c r="O12" s="25"/>
-      <c r="P12" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q12" s="24"/>
+      <c r="N12" s="25"/>
+      <c r="O12" s="26"/>
+      <c r="P12" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q12" s="27"/>
     </row>
     <row r="13" ht="38.25">
       <c r="A13" s="23" t="s">
@@ -3602,17 +3610,17 @@
         <v>79</v>
       </c>
       <c r="L13" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M13" s="23">
         <v>0</v>
       </c>
-      <c r="N13" s="23"/>
-      <c r="O13" s="25"/>
-      <c r="P13" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q13" s="24"/>
+      <c r="N13" s="25"/>
+      <c r="O13" s="26"/>
+      <c r="P13" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q13" s="27"/>
     </row>
     <row r="14" ht="38.25">
       <c r="A14" s="23" t="s">
@@ -3649,17 +3657,17 @@
         <v>84</v>
       </c>
       <c r="L14" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M14" s="23">
         <v>0</v>
       </c>
-      <c r="N14" s="23"/>
-      <c r="O14" s="25"/>
-      <c r="P14" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q14" s="24"/>
+      <c r="N14" s="25"/>
+      <c r="O14" s="26"/>
+      <c r="P14" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q14" s="27"/>
     </row>
     <row r="15" ht="38.25">
       <c r="A15" s="23" t="s">
@@ -3696,17 +3704,17 @@
         <v>87</v>
       </c>
       <c r="L15" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M15" s="23">
         <v>0</v>
       </c>
-      <c r="N15" s="23"/>
-      <c r="O15" s="25"/>
-      <c r="P15" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q15" s="24"/>
+      <c r="N15" s="25"/>
+      <c r="O15" s="26"/>
+      <c r="P15" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q15" s="27"/>
     </row>
     <row r="16" ht="38.25">
       <c r="A16" s="23" t="s">
@@ -3743,17 +3751,17 @@
         <v>90</v>
       </c>
       <c r="L16" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M16" s="23">
         <v>0</v>
       </c>
-      <c r="N16" s="23"/>
-      <c r="O16" s="25"/>
-      <c r="P16" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q16" s="24"/>
+      <c r="N16" s="25"/>
+      <c r="O16" s="26"/>
+      <c r="P16" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q16" s="27"/>
     </row>
     <row r="17" ht="38.25">
       <c r="A17" s="23" t="s">
@@ -3790,17 +3798,17 @@
         <v>93</v>
       </c>
       <c r="L17" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M17" s="23">
         <v>0</v>
       </c>
-      <c r="N17" s="23"/>
-      <c r="O17" s="25"/>
-      <c r="P17" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q17" s="24"/>
+      <c r="N17" s="25"/>
+      <c r="O17" s="26"/>
+      <c r="P17" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q17" s="27"/>
     </row>
     <row r="18" ht="38.25">
       <c r="A18" s="23" t="s">
@@ -3837,17 +3845,17 @@
         <v>96</v>
       </c>
       <c r="L18" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M18" s="23">
         <v>0</v>
       </c>
-      <c r="N18" s="23"/>
-      <c r="O18" s="25"/>
-      <c r="P18" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q18" s="24"/>
+      <c r="N18" s="25"/>
+      <c r="O18" s="26"/>
+      <c r="P18" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q18" s="27"/>
     </row>
     <row r="19" ht="38.25">
       <c r="A19" s="23" t="s">
@@ -3884,17 +3892,17 @@
         <v>99</v>
       </c>
       <c r="L19" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M19" s="23">
         <v>0</v>
       </c>
-      <c r="N19" s="23"/>
-      <c r="O19" s="25"/>
-      <c r="P19" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q19" s="24"/>
+      <c r="N19" s="25"/>
+      <c r="O19" s="26"/>
+      <c r="P19" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q19" s="27"/>
     </row>
     <row r="20" ht="38.25">
       <c r="A20" s="23" t="s">
@@ -3931,17 +3939,17 @@
         <v>102</v>
       </c>
       <c r="L20" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M20" s="23">
         <v>0</v>
       </c>
-      <c r="N20" s="23"/>
-      <c r="O20" s="25"/>
-      <c r="P20" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q20" s="24"/>
+      <c r="N20" s="25"/>
+      <c r="O20" s="26"/>
+      <c r="P20" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q20" s="27"/>
     </row>
     <row r="21" ht="38.25">
       <c r="A21" s="23" t="s">
@@ -3978,17 +3986,17 @@
         <v>105</v>
       </c>
       <c r="L21" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M21" s="23">
         <v>0</v>
       </c>
-      <c r="N21" s="23"/>
-      <c r="O21" s="25"/>
-      <c r="P21" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q21" s="24"/>
+      <c r="N21" s="25"/>
+      <c r="O21" s="26"/>
+      <c r="P21" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q21" s="27"/>
     </row>
     <row r="22" ht="38.25">
       <c r="A22" s="23" t="s">
@@ -4025,17 +4033,17 @@
         <v>108</v>
       </c>
       <c r="L22" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M22" s="23">
         <v>0</v>
       </c>
-      <c r="N22" s="23"/>
-      <c r="O22" s="25"/>
-      <c r="P22" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q22" s="24"/>
+      <c r="N22" s="25"/>
+      <c r="O22" s="26"/>
+      <c r="P22" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q22" s="27"/>
     </row>
     <row r="23" ht="38.25">
       <c r="A23" s="23" t="s">
@@ -4072,17 +4080,17 @@
         <v>111</v>
       </c>
       <c r="L23" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M23" s="23">
         <v>0</v>
       </c>
-      <c r="N23" s="23"/>
-      <c r="O23" s="25"/>
-      <c r="P23" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q23" s="24"/>
+      <c r="N23" s="25"/>
+      <c r="O23" s="26"/>
+      <c r="P23" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q23" s="27"/>
     </row>
     <row r="24" ht="38.25">
       <c r="A24" s="23" t="s">
@@ -4117,17 +4125,17 @@
       </c>
       <c r="K24" s="23"/>
       <c r="L24" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M24" s="23">
         <v>0</v>
       </c>
-      <c r="N24" s="23"/>
-      <c r="O24" s="25"/>
-      <c r="P24" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q24" s="24"/>
+      <c r="N24" s="25"/>
+      <c r="O24" s="26"/>
+      <c r="P24" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q24" s="27"/>
     </row>
     <row r="25" ht="38.25">
       <c r="A25" s="23" t="s">
@@ -4164,17 +4172,17 @@
         <v>117</v>
       </c>
       <c r="L25" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M25" s="23">
         <v>0</v>
       </c>
-      <c r="N25" s="23"/>
-      <c r="O25" s="25"/>
-      <c r="P25" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q25" s="24"/>
+      <c r="N25" s="25"/>
+      <c r="O25" s="26"/>
+      <c r="P25" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q25" s="27"/>
     </row>
     <row r="26" ht="38.25">
       <c r="A26" s="23" t="s">
@@ -4211,17 +4219,17 @@
         <v>121</v>
       </c>
       <c r="L26" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M26" s="23">
         <v>0</v>
       </c>
-      <c r="N26" s="23"/>
-      <c r="O26" s="25"/>
-      <c r="P26" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q26" s="24"/>
+      <c r="N26" s="25"/>
+      <c r="O26" s="26"/>
+      <c r="P26" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q26" s="27"/>
     </row>
     <row r="27" ht="38.25">
       <c r="A27" s="23" t="s">
@@ -4258,17 +4266,17 @@
         <v>124</v>
       </c>
       <c r="L27" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M27" s="23">
         <v>0</v>
       </c>
-      <c r="N27" s="23"/>
-      <c r="O27" s="25"/>
-      <c r="P27" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q27" s="24"/>
+      <c r="N27" s="25"/>
+      <c r="O27" s="26"/>
+      <c r="P27" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q27" s="27"/>
     </row>
     <row r="28" ht="38.25">
       <c r="A28" s="23" t="s">
@@ -4305,17 +4313,17 @@
         <v>127</v>
       </c>
       <c r="L28" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M28" s="23">
         <v>0</v>
       </c>
-      <c r="N28" s="23"/>
-      <c r="O28" s="25"/>
-      <c r="P28" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q28" s="24"/>
+      <c r="N28" s="25"/>
+      <c r="O28" s="26"/>
+      <c r="P28" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q28" s="27"/>
     </row>
     <row r="29" ht="38.25">
       <c r="A29" s="23" t="s">
@@ -4352,17 +4360,17 @@
         <v>130</v>
       </c>
       <c r="L29" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M29" s="23">
         <v>0</v>
       </c>
-      <c r="N29" s="23"/>
-      <c r="O29" s="25"/>
-      <c r="P29" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q29" s="24"/>
+      <c r="N29" s="25"/>
+      <c r="O29" s="26"/>
+      <c r="P29" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q29" s="27"/>
     </row>
     <row r="30" ht="38.25">
       <c r="A30" s="23" t="s">
@@ -4399,17 +4407,17 @@
         <v>133</v>
       </c>
       <c r="L30" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M30" s="23">
         <v>0</v>
       </c>
-      <c r="N30" s="23"/>
-      <c r="O30" s="25"/>
-      <c r="P30" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q30" s="24"/>
+      <c r="N30" s="25"/>
+      <c r="O30" s="26"/>
+      <c r="P30" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q30" s="27"/>
     </row>
     <row r="31" ht="38.25">
       <c r="A31" s="23" t="s">
@@ -4446,17 +4454,17 @@
         <v>136</v>
       </c>
       <c r="L31" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M31" s="23">
         <v>0</v>
       </c>
-      <c r="N31" s="23"/>
-      <c r="O31" s="25"/>
-      <c r="P31" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q31" s="24"/>
+      <c r="N31" s="25"/>
+      <c r="O31" s="26"/>
+      <c r="P31" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q31" s="27"/>
     </row>
     <row r="32" ht="38.25">
       <c r="A32" s="23" t="s">
@@ -4493,17 +4501,17 @@
         <v>139</v>
       </c>
       <c r="L32" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M32" s="23">
         <v>0</v>
       </c>
-      <c r="N32" s="23"/>
-      <c r="O32" s="25"/>
-      <c r="P32" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q32" s="24"/>
+      <c r="N32" s="25"/>
+      <c r="O32" s="26"/>
+      <c r="P32" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q32" s="27"/>
     </row>
     <row r="33" ht="38.25">
       <c r="A33" s="23" t="s">
@@ -4540,17 +4548,17 @@
         <v>142</v>
       </c>
       <c r="L33" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M33" s="23">
         <v>0</v>
       </c>
-      <c r="N33" s="23"/>
-      <c r="O33" s="25"/>
-      <c r="P33" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q33" s="24"/>
+      <c r="N33" s="25"/>
+      <c r="O33" s="26"/>
+      <c r="P33" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q33" s="27"/>
     </row>
     <row r="34" ht="38.25">
       <c r="A34" s="23" t="s">
@@ -4587,17 +4595,17 @@
         <v>145</v>
       </c>
       <c r="L34" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M34" s="23">
         <v>0</v>
       </c>
-      <c r="N34" s="23"/>
-      <c r="O34" s="25"/>
-      <c r="P34" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q34" s="24"/>
+      <c r="N34" s="25"/>
+      <c r="O34" s="26"/>
+      <c r="P34" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q34" s="27"/>
     </row>
     <row r="35" ht="38.25">
       <c r="A35" s="23" t="s">
@@ -4634,17 +4642,17 @@
         <v>148</v>
       </c>
       <c r="L35" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M35" s="23">
         <v>0</v>
       </c>
-      <c r="N35" s="23"/>
-      <c r="O35" s="25"/>
-      <c r="P35" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q35" s="24"/>
+      <c r="N35" s="25"/>
+      <c r="O35" s="26"/>
+      <c r="P35" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q35" s="27"/>
     </row>
     <row r="36" ht="38.25">
       <c r="A36" s="23" t="s">
@@ -4679,17 +4687,17 @@
       </c>
       <c r="K36" s="23"/>
       <c r="L36" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M36" s="23">
         <v>0</v>
       </c>
-      <c r="N36" s="23"/>
-      <c r="O36" s="25"/>
-      <c r="P36" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q36" s="24"/>
+      <c r="N36" s="25"/>
+      <c r="O36" s="26"/>
+      <c r="P36" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q36" s="27"/>
     </row>
     <row r="37" ht="38.25">
       <c r="A37" s="23" t="s">
@@ -4726,17 +4734,17 @@
         <v>154</v>
       </c>
       <c r="L37" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M37" s="23">
         <v>0</v>
       </c>
-      <c r="N37" s="23"/>
-      <c r="O37" s="25"/>
-      <c r="P37" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q37" s="24"/>
+      <c r="N37" s="25"/>
+      <c r="O37" s="26"/>
+      <c r="P37" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q37" s="27"/>
     </row>
     <row r="38" ht="38.25">
       <c r="A38" s="23" t="s">
@@ -4773,17 +4781,17 @@
         <v>159</v>
       </c>
       <c r="L38" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M38" s="23">
         <v>0</v>
       </c>
-      <c r="N38" s="23"/>
-      <c r="O38" s="25"/>
-      <c r="P38" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q38" s="24"/>
+      <c r="N38" s="25"/>
+      <c r="O38" s="26"/>
+      <c r="P38" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q38" s="27"/>
     </row>
     <row r="39" ht="38.25">
       <c r="A39" s="23" t="s">
@@ -4820,17 +4828,17 @@
         <v>162</v>
       </c>
       <c r="L39" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M39" s="23">
         <v>0</v>
       </c>
-      <c r="N39" s="23"/>
-      <c r="O39" s="25"/>
-      <c r="P39" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q39" s="24"/>
+      <c r="N39" s="25"/>
+      <c r="O39" s="26"/>
+      <c r="P39" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q39" s="27"/>
     </row>
     <row r="40" ht="38.25">
       <c r="A40" s="23" t="s">
@@ -4867,17 +4875,17 @@
         <v>165</v>
       </c>
       <c r="L40" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M40" s="23">
         <v>0</v>
       </c>
-      <c r="N40" s="23"/>
-      <c r="O40" s="25"/>
-      <c r="P40" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q40" s="24"/>
+      <c r="N40" s="25"/>
+      <c r="O40" s="26"/>
+      <c r="P40" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q40" s="27"/>
     </row>
     <row r="41" ht="38.25">
       <c r="A41" s="23" t="s">
@@ -4914,17 +4922,17 @@
         <v>168</v>
       </c>
       <c r="L41" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M41" s="23">
         <v>0</v>
       </c>
-      <c r="N41" s="23"/>
-      <c r="O41" s="25"/>
-      <c r="P41" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q41" s="24"/>
+      <c r="N41" s="25"/>
+      <c r="O41" s="26"/>
+      <c r="P41" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q41" s="27"/>
     </row>
     <row r="42" ht="38.25">
       <c r="A42" s="23" t="s">
@@ -4961,17 +4969,17 @@
         <v>171</v>
       </c>
       <c r="L42" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M42" s="23">
         <v>0</v>
       </c>
-      <c r="N42" s="23"/>
-      <c r="O42" s="25"/>
-      <c r="P42" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q42" s="24"/>
+      <c r="N42" s="25"/>
+      <c r="O42" s="26"/>
+      <c r="P42" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q42" s="27"/>
     </row>
     <row r="43" ht="38.25">
       <c r="A43" s="23" t="s">
@@ -5008,17 +5016,17 @@
         <v>174</v>
       </c>
       <c r="L43" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M43" s="23">
         <v>0</v>
       </c>
-      <c r="N43" s="23"/>
-      <c r="O43" s="25"/>
-      <c r="P43" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q43" s="24"/>
+      <c r="N43" s="25"/>
+      <c r="O43" s="26"/>
+      <c r="P43" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q43" s="27"/>
     </row>
     <row r="44" ht="38.25">
       <c r="A44" s="23" t="s">
@@ -5055,17 +5063,17 @@
         <v>177</v>
       </c>
       <c r="L44" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M44" s="23">
         <v>0</v>
       </c>
-      <c r="N44" s="23"/>
-      <c r="O44" s="25"/>
-      <c r="P44" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q44" s="24"/>
+      <c r="N44" s="25"/>
+      <c r="O44" s="26"/>
+      <c r="P44" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q44" s="27"/>
     </row>
     <row r="45" ht="38.25">
       <c r="A45" s="23" t="s">
@@ -5102,17 +5110,17 @@
         <v>180</v>
       </c>
       <c r="L45" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M45" s="23">
         <v>0</v>
       </c>
-      <c r="N45" s="23"/>
-      <c r="O45" s="25"/>
-      <c r="P45" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q45" s="24"/>
+      <c r="N45" s="25"/>
+      <c r="O45" s="26"/>
+      <c r="P45" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q45" s="27"/>
     </row>
     <row r="46" ht="38.25">
       <c r="A46" s="23" t="s">
@@ -5149,17 +5157,17 @@
         <v>183</v>
       </c>
       <c r="L46" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M46" s="23">
         <v>0</v>
       </c>
-      <c r="N46" s="23"/>
-      <c r="O46" s="25"/>
-      <c r="P46" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q46" s="24"/>
+      <c r="N46" s="25"/>
+      <c r="O46" s="26"/>
+      <c r="P46" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q46" s="27"/>
     </row>
     <row r="47" ht="38.25">
       <c r="A47" s="23" t="s">
@@ -5196,17 +5204,17 @@
         <v>186</v>
       </c>
       <c r="L47" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M47" s="23">
         <v>0</v>
       </c>
-      <c r="N47" s="23"/>
-      <c r="O47" s="25"/>
-      <c r="P47" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q47" s="24"/>
+      <c r="N47" s="25"/>
+      <c r="O47" s="26"/>
+      <c r="P47" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q47" s="27"/>
     </row>
     <row r="48" ht="38.25">
       <c r="A48" s="23" t="s">
@@ -5243,17 +5251,17 @@
         <v>189</v>
       </c>
       <c r="L48" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M48" s="23">
         <v>0</v>
       </c>
-      <c r="N48" s="23"/>
-      <c r="O48" s="25"/>
-      <c r="P48" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q48" s="24"/>
+      <c r="N48" s="25"/>
+      <c r="O48" s="26"/>
+      <c r="P48" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q48" s="27"/>
     </row>
     <row r="49" ht="38.25">
       <c r="A49" s="23" t="s">
@@ -5290,17 +5298,17 @@
         <v>192</v>
       </c>
       <c r="L49" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M49" s="23">
         <v>0</v>
       </c>
-      <c r="N49" s="23"/>
-      <c r="O49" s="25"/>
-      <c r="P49" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q49" s="24"/>
+      <c r="N49" s="25"/>
+      <c r="O49" s="26"/>
+      <c r="P49" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q49" s="27"/>
     </row>
     <row r="50" ht="38.25">
       <c r="A50" s="23" t="s">
@@ -5335,17 +5343,17 @@
       </c>
       <c r="K50" s="23"/>
       <c r="L50" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M50" s="23">
         <v>0</v>
       </c>
-      <c r="N50" s="23"/>
-      <c r="O50" s="25"/>
-      <c r="P50" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q50" s="24"/>
+      <c r="N50" s="25"/>
+      <c r="O50" s="26"/>
+      <c r="P50" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q50" s="27"/>
     </row>
     <row r="51" ht="38.25">
       <c r="A51" s="23" t="s">
@@ -5382,17 +5390,17 @@
         <v>198</v>
       </c>
       <c r="L51" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M51" s="23">
         <v>0</v>
       </c>
-      <c r="N51" s="23"/>
-      <c r="O51" s="25"/>
-      <c r="P51" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q51" s="24"/>
+      <c r="N51" s="25"/>
+      <c r="O51" s="26"/>
+      <c r="P51" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q51" s="27"/>
     </row>
     <row r="52" ht="38.25">
       <c r="A52" s="23" t="s">
@@ -5429,17 +5437,17 @@
         <v>204</v>
       </c>
       <c r="L52" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M52" s="23">
         <v>0</v>
       </c>
-      <c r="N52" s="23"/>
-      <c r="O52" s="25"/>
-      <c r="P52" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q52" s="24"/>
+      <c r="N52" s="25"/>
+      <c r="O52" s="26"/>
+      <c r="P52" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q52" s="27"/>
     </row>
     <row r="53" ht="38.25">
       <c r="A53" s="23" t="s">
@@ -5476,17 +5484,17 @@
         <v>207</v>
       </c>
       <c r="L53" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M53" s="23">
         <v>0</v>
       </c>
-      <c r="N53" s="23"/>
-      <c r="O53" s="25"/>
-      <c r="P53" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q53" s="24"/>
+      <c r="N53" s="25"/>
+      <c r="O53" s="26"/>
+      <c r="P53" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q53" s="27"/>
     </row>
     <row r="54" ht="38.25">
       <c r="A54" s="23" t="s">
@@ -5523,17 +5531,17 @@
         <v>210</v>
       </c>
       <c r="L54" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M54" s="23">
         <v>0</v>
       </c>
-      <c r="N54" s="23"/>
-      <c r="O54" s="25"/>
-      <c r="P54" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q54" s="24"/>
+      <c r="N54" s="25"/>
+      <c r="O54" s="26"/>
+      <c r="P54" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q54" s="27"/>
     </row>
     <row r="55" ht="38.25">
       <c r="A55" s="23" t="s">
@@ -5570,17 +5578,17 @@
         <v>213</v>
       </c>
       <c r="L55" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M55" s="23">
         <v>0</v>
       </c>
-      <c r="N55" s="23"/>
-      <c r="O55" s="25"/>
-      <c r="P55" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q55" s="24"/>
+      <c r="N55" s="25"/>
+      <c r="O55" s="26"/>
+      <c r="P55" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q55" s="27"/>
     </row>
     <row r="56" ht="38.25">
       <c r="A56" s="23" t="s">
@@ -5617,17 +5625,17 @@
         <v>216</v>
       </c>
       <c r="L56" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M56" s="23">
         <v>0</v>
       </c>
-      <c r="N56" s="23"/>
-      <c r="O56" s="25"/>
-      <c r="P56" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q56" s="24"/>
+      <c r="N56" s="25"/>
+      <c r="O56" s="26"/>
+      <c r="P56" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q56" s="27"/>
     </row>
     <row r="57" ht="38.25">
       <c r="A57" s="23" t="s">
@@ -5664,17 +5672,17 @@
         <v>219</v>
       </c>
       <c r="L57" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M57" s="23">
         <v>0</v>
       </c>
-      <c r="N57" s="23"/>
-      <c r="O57" s="25"/>
-      <c r="P57" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q57" s="24"/>
+      <c r="N57" s="25"/>
+      <c r="O57" s="26"/>
+      <c r="P57" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q57" s="27"/>
     </row>
     <row r="58" ht="38.25">
       <c r="A58" s="23" t="s">
@@ -5709,17 +5717,17 @@
       </c>
       <c r="K58" s="23"/>
       <c r="L58" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M58" s="23">
         <v>0</v>
       </c>
-      <c r="N58" s="23"/>
-      <c r="O58" s="25"/>
-      <c r="P58" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q58" s="24"/>
+      <c r="N58" s="25"/>
+      <c r="O58" s="26"/>
+      <c r="P58" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q58" s="27"/>
     </row>
     <row r="59" ht="38.25">
       <c r="A59" s="23" t="s">
@@ -5756,17 +5764,17 @@
         <v>225</v>
       </c>
       <c r="L59" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M59" s="23">
         <v>0</v>
       </c>
-      <c r="N59" s="23"/>
-      <c r="O59" s="25"/>
-      <c r="P59" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q59" s="24"/>
+      <c r="N59" s="25"/>
+      <c r="O59" s="26"/>
+      <c r="P59" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q59" s="27"/>
     </row>
     <row r="60" ht="38.25">
       <c r="A60" s="23" t="s">
@@ -5803,17 +5811,17 @@
         <v>229</v>
       </c>
       <c r="L60" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M60" s="23">
         <v>0</v>
       </c>
-      <c r="N60" s="23"/>
-      <c r="O60" s="25"/>
-      <c r="P60" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q60" s="24"/>
+      <c r="N60" s="25"/>
+      <c r="O60" s="26"/>
+      <c r="P60" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q60" s="27"/>
     </row>
     <row r="61" ht="38.25">
       <c r="A61" s="23" t="s">
@@ -5850,17 +5858,17 @@
         <v>232</v>
       </c>
       <c r="L61" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M61" s="23">
         <v>0</v>
       </c>
-      <c r="N61" s="23"/>
-      <c r="O61" s="25"/>
-      <c r="P61" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q61" s="24"/>
+      <c r="N61" s="25"/>
+      <c r="O61" s="26"/>
+      <c r="P61" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q61" s="27"/>
     </row>
     <row r="62" ht="38.25">
       <c r="A62" s="23" t="s">
@@ -5897,17 +5905,17 @@
         <v>235</v>
       </c>
       <c r="L62" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M62" s="23">
         <v>0</v>
       </c>
-      <c r="N62" s="23"/>
-      <c r="O62" s="25"/>
-      <c r="P62" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q62" s="24"/>
+      <c r="N62" s="25"/>
+      <c r="O62" s="26"/>
+      <c r="P62" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q62" s="27"/>
     </row>
     <row r="63" ht="38.25">
       <c r="A63" s="23" t="s">
@@ -5944,17 +5952,17 @@
         <v>238</v>
       </c>
       <c r="L63" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M63" s="23">
         <v>0</v>
       </c>
-      <c r="N63" s="23"/>
-      <c r="O63" s="25"/>
-      <c r="P63" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q63" s="24"/>
+      <c r="N63" s="25"/>
+      <c r="O63" s="26"/>
+      <c r="P63" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q63" s="27"/>
     </row>
     <row r="64" ht="38.25">
       <c r="A64" s="23" t="s">
@@ -5991,17 +5999,17 @@
         <v>241</v>
       </c>
       <c r="L64" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M64" s="23">
         <v>0</v>
       </c>
-      <c r="N64" s="23"/>
-      <c r="O64" s="25"/>
-      <c r="P64" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q64" s="24"/>
+      <c r="N64" s="25"/>
+      <c r="O64" s="26"/>
+      <c r="P64" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q64" s="27"/>
     </row>
     <row r="65" ht="41.75">
       <c r="A65" s="23" t="s">
@@ -6038,17 +6046,17 @@
         <v>244</v>
       </c>
       <c r="L65" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M65" s="23">
         <v>0</v>
       </c>
-      <c r="N65" s="23"/>
-      <c r="O65" s="25"/>
-      <c r="P65" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q65" s="24"/>
+      <c r="N65" s="25"/>
+      <c r="O65" s="26"/>
+      <c r="P65" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q65" s="27"/>
     </row>
     <row r="66" ht="41.75">
       <c r="A66" s="23" t="s">
@@ -6085,17 +6093,17 @@
         <v>247</v>
       </c>
       <c r="L66" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M66" s="23">
         <v>0</v>
       </c>
-      <c r="N66" s="23"/>
-      <c r="O66" s="25"/>
-      <c r="P66" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q66" s="24"/>
+      <c r="N66" s="25"/>
+      <c r="O66" s="26"/>
+      <c r="P66" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q66" s="27"/>
     </row>
     <row r="67" ht="41.75">
       <c r="A67" s="23" t="s">
@@ -6132,17 +6140,17 @@
         <v>250</v>
       </c>
       <c r="L67" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M67" s="23">
         <v>0</v>
       </c>
-      <c r="N67" s="23"/>
-      <c r="O67" s="25"/>
-      <c r="P67" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q67" s="24"/>
+      <c r="N67" s="25"/>
+      <c r="O67" s="26"/>
+      <c r="P67" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q67" s="27"/>
     </row>
     <row r="68" ht="41.75">
       <c r="A68" s="23" t="s">
@@ -6179,17 +6187,17 @@
         <v>253</v>
       </c>
       <c r="L68" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M68" s="23">
         <v>0</v>
       </c>
-      <c r="N68" s="23"/>
-      <c r="O68" s="25"/>
-      <c r="P68" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q68" s="24"/>
+      <c r="N68" s="25"/>
+      <c r="O68" s="26"/>
+      <c r="P68" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q68" s="27"/>
     </row>
     <row r="69" ht="41.75">
       <c r="A69" s="23" t="s">
@@ -6226,17 +6234,17 @@
         <v>256</v>
       </c>
       <c r="L69" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M69" s="23">
         <v>0</v>
       </c>
-      <c r="N69" s="23"/>
-      <c r="O69" s="25"/>
-      <c r="P69" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q69" s="24"/>
+      <c r="N69" s="25"/>
+      <c r="O69" s="26"/>
+      <c r="P69" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q69" s="27"/>
     </row>
     <row r="70" ht="41.75">
       <c r="A70" s="23" t="s">
@@ -6271,17 +6279,17 @@
       </c>
       <c r="K70" s="23"/>
       <c r="L70" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M70" s="23">
         <v>0</v>
       </c>
-      <c r="N70" s="23"/>
-      <c r="O70" s="25"/>
-      <c r="P70" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q70" s="24"/>
+      <c r="N70" s="25"/>
+      <c r="O70" s="26"/>
+      <c r="P70" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q70" s="27"/>
     </row>
     <row r="71" ht="41.75">
       <c r="A71" s="23" t="s">
@@ -6318,17 +6326,17 @@
         <v>262</v>
       </c>
       <c r="L71" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M71" s="23">
         <v>0</v>
       </c>
-      <c r="N71" s="23"/>
-      <c r="O71" s="25"/>
-      <c r="P71" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q71" s="24"/>
+      <c r="N71" s="25"/>
+      <c r="O71" s="26"/>
+      <c r="P71" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q71" s="27"/>
     </row>
     <row r="72" ht="41.75">
       <c r="A72" s="23" t="s">
@@ -6365,17 +6373,17 @@
         <v>266</v>
       </c>
       <c r="L72" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M72" s="23">
         <v>0</v>
       </c>
-      <c r="N72" s="23"/>
-      <c r="O72" s="25"/>
-      <c r="P72" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q72" s="24"/>
+      <c r="N72" s="25"/>
+      <c r="O72" s="26"/>
+      <c r="P72" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q72" s="27"/>
     </row>
     <row r="73" ht="41.75">
       <c r="A73" s="23" t="s">
@@ -6412,17 +6420,17 @@
         <v>269</v>
       </c>
       <c r="L73" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M73" s="23">
         <v>0</v>
       </c>
-      <c r="N73" s="23"/>
-      <c r="O73" s="25"/>
-      <c r="P73" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q73" s="24"/>
+      <c r="N73" s="25"/>
+      <c r="O73" s="26"/>
+      <c r="P73" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q73" s="27"/>
     </row>
     <row r="74" ht="41.75">
       <c r="A74" s="23" t="s">
@@ -6459,17 +6467,17 @@
         <v>272</v>
       </c>
       <c r="L74" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M74" s="23">
         <v>0</v>
       </c>
-      <c r="N74" s="23"/>
-      <c r="O74" s="25"/>
-      <c r="P74" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q74" s="24"/>
+      <c r="N74" s="25"/>
+      <c r="O74" s="26"/>
+      <c r="P74" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q74" s="27"/>
     </row>
     <row r="75" ht="41.75">
       <c r="A75" s="23" t="s">
@@ -6506,17 +6514,17 @@
         <v>275</v>
       </c>
       <c r="L75" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M75" s="23">
         <v>0</v>
       </c>
-      <c r="N75" s="23"/>
-      <c r="O75" s="25"/>
-      <c r="P75" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q75" s="24"/>
+      <c r="N75" s="25"/>
+      <c r="O75" s="26"/>
+      <c r="P75" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q75" s="27"/>
     </row>
     <row r="76" ht="41.75">
       <c r="A76" s="23" t="s">
@@ -6553,17 +6561,17 @@
         <v>278</v>
       </c>
       <c r="L76" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M76" s="23">
         <v>0</v>
       </c>
-      <c r="N76" s="23"/>
-      <c r="O76" s="25"/>
-      <c r="P76" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q76" s="24"/>
+      <c r="N76" s="25"/>
+      <c r="O76" s="26"/>
+      <c r="P76" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q76" s="27"/>
     </row>
     <row r="77" ht="41.75">
       <c r="A77" s="23" t="s">
@@ -6600,17 +6608,17 @@
         <v>281</v>
       </c>
       <c r="L77" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M77" s="23">
         <v>0</v>
       </c>
-      <c r="N77" s="23"/>
-      <c r="O77" s="25"/>
-      <c r="P77" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q77" s="24"/>
+      <c r="N77" s="25"/>
+      <c r="O77" s="26"/>
+      <c r="P77" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q77" s="27"/>
     </row>
     <row r="78" ht="41.75">
       <c r="A78" s="23" t="s">
@@ -6647,17 +6655,17 @@
         <v>284</v>
       </c>
       <c r="L78" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M78" s="23">
         <v>0</v>
       </c>
-      <c r="N78" s="23"/>
-      <c r="O78" s="25"/>
-      <c r="P78" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q78" s="24"/>
+      <c r="N78" s="25"/>
+      <c r="O78" s="26"/>
+      <c r="P78" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q78" s="27"/>
     </row>
     <row r="79" ht="41.75">
       <c r="A79" s="23" t="s">
@@ -6692,17 +6700,17 @@
       </c>
       <c r="K79" s="23"/>
       <c r="L79" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M79" s="23">
         <v>0</v>
       </c>
-      <c r="N79" s="23"/>
-      <c r="O79" s="25"/>
-      <c r="P79" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q79" s="24"/>
+      <c r="N79" s="25"/>
+      <c r="O79" s="26"/>
+      <c r="P79" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q79" s="27"/>
     </row>
     <row r="80" ht="41.75">
       <c r="A80" s="23" t="s">
@@ -6739,17 +6747,17 @@
         <v>290</v>
       </c>
       <c r="L80" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M80" s="23">
         <v>0</v>
       </c>
-      <c r="N80" s="23"/>
-      <c r="O80" s="25"/>
-      <c r="P80" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q80" s="24"/>
+      <c r="N80" s="25"/>
+      <c r="O80" s="26"/>
+      <c r="P80" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q80" s="27"/>
     </row>
     <row r="81" ht="41.75">
       <c r="A81" s="23" t="s">
@@ -6786,17 +6794,17 @@
         <v>294</v>
       </c>
       <c r="L81" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M81" s="23">
         <v>0</v>
       </c>
-      <c r="N81" s="23"/>
-      <c r="O81" s="25"/>
-      <c r="P81" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q81" s="24"/>
+      <c r="N81" s="25"/>
+      <c r="O81" s="26"/>
+      <c r="P81" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q81" s="27"/>
     </row>
     <row r="82" ht="41.75">
       <c r="A82" s="23" t="s">
@@ -6833,17 +6841,17 @@
         <v>297</v>
       </c>
       <c r="L82" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M82" s="23">
         <v>0</v>
       </c>
-      <c r="N82" s="23"/>
-      <c r="O82" s="25"/>
-      <c r="P82" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q82" s="24"/>
+      <c r="N82" s="25"/>
+      <c r="O82" s="26"/>
+      <c r="P82" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q82" s="27"/>
     </row>
     <row r="83" ht="41.75">
       <c r="A83" s="23" t="s">
@@ -6880,17 +6888,17 @@
         <v>300</v>
       </c>
       <c r="L83" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M83" s="23">
         <v>0</v>
       </c>
-      <c r="N83" s="23"/>
-      <c r="O83" s="25"/>
-      <c r="P83" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q83" s="24"/>
+      <c r="N83" s="25"/>
+      <c r="O83" s="26"/>
+      <c r="P83" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q83" s="27"/>
     </row>
     <row r="84" ht="41.75">
       <c r="A84" s="23" t="s">
@@ -6927,17 +6935,17 @@
         <v>303</v>
       </c>
       <c r="L84" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M84" s="23">
         <v>0</v>
       </c>
-      <c r="N84" s="23"/>
-      <c r="O84" s="25"/>
-      <c r="P84" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q84" s="24"/>
+      <c r="N84" s="25"/>
+      <c r="O84" s="26"/>
+      <c r="P84" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q84" s="27"/>
     </row>
     <row r="85" ht="41.75">
       <c r="A85" s="23" t="s">
@@ -6974,17 +6982,17 @@
         <v>306</v>
       </c>
       <c r="L85" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M85" s="23">
         <v>0</v>
       </c>
-      <c r="N85" s="23"/>
-      <c r="O85" s="25"/>
-      <c r="P85" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q85" s="24"/>
+      <c r="N85" s="25"/>
+      <c r="O85" s="26"/>
+      <c r="P85" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q85" s="27"/>
     </row>
     <row r="86" ht="41.75">
       <c r="A86" s="23" t="s">
@@ -7021,17 +7029,17 @@
         <v>309</v>
       </c>
       <c r="L86" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M86" s="23">
         <v>0</v>
       </c>
-      <c r="N86" s="23"/>
-      <c r="O86" s="25"/>
-      <c r="P86" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q86" s="24"/>
+      <c r="N86" s="25"/>
+      <c r="O86" s="26"/>
+      <c r="P86" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q86" s="27"/>
     </row>
     <row r="87" ht="41.75">
       <c r="A87" s="23" t="s">
@@ -7068,17 +7076,17 @@
         <v>312</v>
       </c>
       <c r="L87" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M87" s="23">
         <v>0</v>
       </c>
-      <c r="N87" s="23"/>
-      <c r="O87" s="25"/>
-      <c r="P87" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q87" s="24"/>
+      <c r="N87" s="25"/>
+      <c r="O87" s="26"/>
+      <c r="P87" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q87" s="27"/>
     </row>
     <row r="88" ht="41.75">
       <c r="A88" s="23" t="s">
@@ -7115,17 +7123,17 @@
         <v>315</v>
       </c>
       <c r="L88" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M88" s="23">
         <v>0</v>
       </c>
-      <c r="N88" s="23"/>
-      <c r="O88" s="25"/>
-      <c r="P88" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q88" s="24"/>
+      <c r="N88" s="25"/>
+      <c r="O88" s="26"/>
+      <c r="P88" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q88" s="27"/>
     </row>
     <row r="89" ht="41.75">
       <c r="A89" s="23" t="s">
@@ -7160,17 +7168,17 @@
       </c>
       <c r="K89" s="23"/>
       <c r="L89" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M89" s="23">
         <v>0</v>
       </c>
-      <c r="N89" s="23"/>
-      <c r="O89" s="25"/>
-      <c r="P89" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q89" s="24"/>
+      <c r="N89" s="25"/>
+      <c r="O89" s="26"/>
+      <c r="P89" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q89" s="27"/>
     </row>
     <row r="90" ht="41.75">
       <c r="A90" s="23" t="s">
@@ -7207,17 +7215,17 @@
         <v>321</v>
       </c>
       <c r="L90" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M90" s="23">
         <v>0</v>
       </c>
-      <c r="N90" s="23"/>
-      <c r="O90" s="25"/>
-      <c r="P90" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q90" s="24"/>
+      <c r="N90" s="25"/>
+      <c r="O90" s="26"/>
+      <c r="P90" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q90" s="27"/>
     </row>
     <row r="91" ht="41.75">
       <c r="A91" s="23" t="s">
@@ -7254,17 +7262,17 @@
         <v>325</v>
       </c>
       <c r="L91" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M91" s="23">
         <v>0</v>
       </c>
-      <c r="N91" s="23"/>
-      <c r="O91" s="25"/>
-      <c r="P91" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q91" s="24"/>
+      <c r="N91" s="25"/>
+      <c r="O91" s="26"/>
+      <c r="P91" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q91" s="27"/>
     </row>
     <row r="92" ht="41.75">
       <c r="A92" s="23" t="s">
@@ -7301,17 +7309,17 @@
         <v>328</v>
       </c>
       <c r="L92" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M92" s="23">
         <v>0</v>
       </c>
-      <c r="N92" s="23"/>
-      <c r="O92" s="25"/>
-      <c r="P92" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q92" s="24"/>
+      <c r="N92" s="25"/>
+      <c r="O92" s="26"/>
+      <c r="P92" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q92" s="27"/>
     </row>
     <row r="93" ht="41.75">
       <c r="A93" s="23" t="s">
@@ -7348,17 +7356,17 @@
         <v>331</v>
       </c>
       <c r="L93" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M93" s="23">
         <v>0</v>
       </c>
-      <c r="N93" s="23"/>
-      <c r="O93" s="25"/>
-      <c r="P93" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q93" s="24"/>
+      <c r="N93" s="25"/>
+      <c r="O93" s="26"/>
+      <c r="P93" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q93" s="27"/>
     </row>
     <row r="94" ht="41.75">
       <c r="A94" s="23" t="s">
@@ -7395,17 +7403,17 @@
         <v>334</v>
       </c>
       <c r="L94" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M94" s="23">
         <v>0</v>
       </c>
-      <c r="N94" s="23"/>
-      <c r="O94" s="25"/>
-      <c r="P94" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q94" s="24"/>
+      <c r="N94" s="25"/>
+      <c r="O94" s="26"/>
+      <c r="P94" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q94" s="27"/>
     </row>
     <row r="95" ht="41.75">
       <c r="A95" s="23" t="s">
@@ -7442,17 +7450,17 @@
         <v>337</v>
       </c>
       <c r="L95" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M95" s="23">
         <v>0</v>
       </c>
-      <c r="N95" s="23"/>
-      <c r="O95" s="25"/>
-      <c r="P95" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q95" s="24"/>
+      <c r="N95" s="25"/>
+      <c r="O95" s="26"/>
+      <c r="P95" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q95" s="27"/>
     </row>
     <row r="96" ht="41.75">
       <c r="A96" s="23" t="s">
@@ -7489,17 +7497,17 @@
         <v>340</v>
       </c>
       <c r="L96" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M96" s="23">
         <v>0</v>
       </c>
-      <c r="N96" s="23"/>
-      <c r="O96" s="25"/>
-      <c r="P96" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q96" s="24"/>
+      <c r="N96" s="25"/>
+      <c r="O96" s="26"/>
+      <c r="P96" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q96" s="27"/>
     </row>
     <row r="97" ht="41.75">
       <c r="A97" s="23" t="s">
@@ -7536,17 +7544,17 @@
         <v>343</v>
       </c>
       <c r="L97" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M97" s="23">
         <v>0</v>
       </c>
-      <c r="N97" s="23"/>
-      <c r="O97" s="25"/>
-      <c r="P97" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q97" s="24"/>
+      <c r="N97" s="25"/>
+      <c r="O97" s="26"/>
+      <c r="P97" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q97" s="27"/>
     </row>
     <row r="98" ht="41.75">
       <c r="A98" s="23" t="s">
@@ -7581,17 +7589,17 @@
       </c>
       <c r="K98" s="23"/>
       <c r="L98" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M98" s="23">
         <v>0</v>
       </c>
-      <c r="N98" s="23"/>
-      <c r="O98" s="25"/>
-      <c r="P98" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q98" s="24"/>
+      <c r="N98" s="25"/>
+      <c r="O98" s="26"/>
+      <c r="P98" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q98" s="27"/>
     </row>
     <row r="99" ht="41.75">
       <c r="A99" s="23" t="s">
@@ -7628,17 +7636,17 @@
         <v>349</v>
       </c>
       <c r="L99" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M99" s="23">
         <v>0</v>
       </c>
-      <c r="N99" s="23"/>
-      <c r="O99" s="25"/>
-      <c r="P99" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q99" s="24"/>
+      <c r="N99" s="25"/>
+      <c r="O99" s="26"/>
+      <c r="P99" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q99" s="27"/>
     </row>
     <row r="100" ht="41.75">
       <c r="A100" s="23" t="s">
@@ -7675,17 +7683,17 @@
         <v>353</v>
       </c>
       <c r="L100" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M100" s="23">
         <v>0</v>
       </c>
-      <c r="N100" s="23"/>
-      <c r="O100" s="25"/>
-      <c r="P100" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q100" s="24"/>
+      <c r="N100" s="25"/>
+      <c r="O100" s="26"/>
+      <c r="P100" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q100" s="27"/>
     </row>
     <row r="101" ht="41.75">
       <c r="A101" s="23" t="s">
@@ -7722,17 +7730,17 @@
         <v>356</v>
       </c>
       <c r="L101" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M101" s="23">
         <v>0</v>
       </c>
-      <c r="N101" s="23"/>
-      <c r="O101" s="25"/>
-      <c r="P101" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q101" s="24"/>
+      <c r="N101" s="25"/>
+      <c r="O101" s="26"/>
+      <c r="P101" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q101" s="27"/>
     </row>
     <row r="102" ht="41.75">
       <c r="A102" s="23" t="s">
@@ -7769,17 +7777,17 @@
         <v>359</v>
       </c>
       <c r="L102" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M102" s="23">
         <v>0</v>
       </c>
-      <c r="N102" s="23"/>
-      <c r="O102" s="25"/>
-      <c r="P102" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q102" s="24"/>
+      <c r="N102" s="25"/>
+      <c r="O102" s="26"/>
+      <c r="P102" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q102" s="27"/>
     </row>
     <row r="103" ht="41.75">
       <c r="A103" s="23" t="s">
@@ -7816,17 +7824,17 @@
         <v>362</v>
       </c>
       <c r="L103" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M103" s="23">
         <v>0</v>
       </c>
-      <c r="N103" s="23"/>
-      <c r="O103" s="25"/>
-      <c r="P103" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q103" s="24"/>
+      <c r="N103" s="25"/>
+      <c r="O103" s="26"/>
+      <c r="P103" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q103" s="27"/>
     </row>
     <row r="104" ht="41.75">
       <c r="A104" s="23" t="s">
@@ -7863,17 +7871,17 @@
         <v>365</v>
       </c>
       <c r="L104" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M104" s="23">
         <v>0</v>
       </c>
-      <c r="N104" s="23"/>
-      <c r="O104" s="25"/>
-      <c r="P104" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q104" s="24"/>
+      <c r="N104" s="25"/>
+      <c r="O104" s="26"/>
+      <c r="P104" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q104" s="27"/>
     </row>
     <row r="105" ht="41.75">
       <c r="A105" s="23" t="s">
@@ -7908,17 +7916,17 @@
       </c>
       <c r="K105" s="23"/>
       <c r="L105" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M105" s="23">
         <v>0</v>
       </c>
-      <c r="N105" s="23"/>
-      <c r="O105" s="25"/>
-      <c r="P105" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q105" s="24"/>
+      <c r="N105" s="25"/>
+      <c r="O105" s="26"/>
+      <c r="P105" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q105" s="27"/>
     </row>
     <row r="106" ht="41.75">
       <c r="A106" s="23" t="s">
@@ -7955,17 +7963,17 @@
         <v>371</v>
       </c>
       <c r="L106" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M106" s="23">
         <v>0</v>
       </c>
-      <c r="N106" s="23"/>
-      <c r="O106" s="25"/>
-      <c r="P106" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q106" s="24"/>
+      <c r="N106" s="25"/>
+      <c r="O106" s="26"/>
+      <c r="P106" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q106" s="27"/>
     </row>
     <row r="107" ht="41.75">
       <c r="A107" s="23" t="s">
@@ -8002,17 +8010,17 @@
         <v>376</v>
       </c>
       <c r="L107" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M107" s="23">
         <v>0</v>
       </c>
-      <c r="N107" s="23"/>
-      <c r="O107" s="25"/>
-      <c r="P107" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q107" s="24"/>
+      <c r="N107" s="25"/>
+      <c r="O107" s="26"/>
+      <c r="P107" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q107" s="27"/>
     </row>
     <row r="108" ht="41.75">
       <c r="A108" s="23" t="s">
@@ -8049,17 +8057,17 @@
         <v>379</v>
       </c>
       <c r="L108" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M108" s="23">
         <v>0</v>
       </c>
-      <c r="N108" s="23"/>
-      <c r="O108" s="25"/>
-      <c r="P108" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q108" s="24"/>
+      <c r="N108" s="25"/>
+      <c r="O108" s="26"/>
+      <c r="P108" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q108" s="27"/>
     </row>
     <row r="109" ht="41.75">
       <c r="A109" s="23" t="s">
@@ -8096,17 +8104,17 @@
         <v>382</v>
       </c>
       <c r="L109" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M109" s="23">
         <v>0</v>
       </c>
-      <c r="N109" s="23"/>
-      <c r="O109" s="25"/>
-      <c r="P109" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q109" s="24"/>
+      <c r="N109" s="25"/>
+      <c r="O109" s="26"/>
+      <c r="P109" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q109" s="27"/>
     </row>
     <row r="110" ht="41.75">
       <c r="A110" s="23" t="s">
@@ -8143,17 +8151,17 @@
         <v>385</v>
       </c>
       <c r="L110" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M110" s="23">
         <v>0</v>
       </c>
-      <c r="N110" s="23"/>
-      <c r="O110" s="25"/>
-      <c r="P110" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q110" s="24"/>
+      <c r="N110" s="25"/>
+      <c r="O110" s="26"/>
+      <c r="P110" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q110" s="27"/>
     </row>
     <row r="111" ht="41.75">
       <c r="A111" s="23" t="s">
@@ -8190,17 +8198,17 @@
         <v>388</v>
       </c>
       <c r="L111" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M111" s="23">
         <v>0</v>
       </c>
-      <c r="N111" s="23"/>
-      <c r="O111" s="25"/>
-      <c r="P111" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q111" s="24"/>
+      <c r="N111" s="25"/>
+      <c r="O111" s="26"/>
+      <c r="P111" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q111" s="27"/>
     </row>
     <row r="112" ht="41.75">
       <c r="A112" s="23" t="s">
@@ -8237,17 +8245,17 @@
         <v>391</v>
       </c>
       <c r="L112" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M112" s="23">
         <v>0</v>
       </c>
-      <c r="N112" s="23"/>
-      <c r="O112" s="25"/>
-      <c r="P112" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q112" s="24"/>
+      <c r="N112" s="25"/>
+      <c r="O112" s="26"/>
+      <c r="P112" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q112" s="27"/>
     </row>
     <row r="113" ht="41.75">
       <c r="A113" s="23" t="s">
@@ -8284,17 +8292,17 @@
         <v>394</v>
       </c>
       <c r="L113" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M113" s="23">
         <v>0</v>
       </c>
-      <c r="N113" s="23"/>
-      <c r="O113" s="25"/>
-      <c r="P113" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q113" s="24"/>
+      <c r="N113" s="25"/>
+      <c r="O113" s="26"/>
+      <c r="P113" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q113" s="27"/>
     </row>
     <row r="114" ht="41.75">
       <c r="A114" s="23" t="s">
@@ -8331,17 +8339,17 @@
         <v>397</v>
       </c>
       <c r="L114" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M114" s="23">
         <v>0</v>
       </c>
-      <c r="N114" s="23"/>
-      <c r="O114" s="25"/>
-      <c r="P114" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q114" s="24"/>
+      <c r="N114" s="25"/>
+      <c r="O114" s="26"/>
+      <c r="P114" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q114" s="27"/>
     </row>
     <row r="115" ht="41.75">
       <c r="A115" s="23" t="s">
@@ -8376,17 +8384,17 @@
       </c>
       <c r="K115" s="23"/>
       <c r="L115" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M115" s="23">
         <v>0</v>
       </c>
-      <c r="N115" s="23"/>
-      <c r="O115" s="25"/>
-      <c r="P115" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q115" s="24"/>
+      <c r="N115" s="25"/>
+      <c r="O115" s="26"/>
+      <c r="P115" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q115" s="27"/>
     </row>
     <row r="116" ht="41.75">
       <c r="A116" s="23" t="s">
@@ -8423,17 +8431,17 @@
         <v>403</v>
       </c>
       <c r="L116" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M116" s="23">
         <v>0</v>
       </c>
-      <c r="N116" s="23"/>
-      <c r="O116" s="25"/>
-      <c r="P116" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q116" s="24"/>
+      <c r="N116" s="25"/>
+      <c r="O116" s="26"/>
+      <c r="P116" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q116" s="27"/>
     </row>
     <row r="117" ht="41.75">
       <c r="A117" s="23" t="s">
@@ -8470,17 +8478,17 @@
         <v>408</v>
       </c>
       <c r="L117" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M117" s="23">
         <v>0</v>
       </c>
-      <c r="N117" s="23"/>
-      <c r="O117" s="25"/>
-      <c r="P117" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q117" s="24"/>
+      <c r="N117" s="25"/>
+      <c r="O117" s="26"/>
+      <c r="P117" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q117" s="27"/>
     </row>
     <row r="118" ht="41.75">
       <c r="A118" s="23" t="s">
@@ -8517,17 +8525,17 @@
         <v>411</v>
       </c>
       <c r="L118" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M118" s="23">
         <v>0</v>
       </c>
-      <c r="N118" s="23"/>
-      <c r="O118" s="25"/>
-      <c r="P118" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q118" s="24"/>
+      <c r="N118" s="25"/>
+      <c r="O118" s="26"/>
+      <c r="P118" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q118" s="27"/>
     </row>
     <row r="119" ht="41.75">
       <c r="A119" s="23" t="s">
@@ -8564,17 +8572,17 @@
         <v>414</v>
       </c>
       <c r="L119" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M119" s="23">
         <v>0</v>
       </c>
-      <c r="N119" s="23"/>
-      <c r="O119" s="25"/>
-      <c r="P119" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q119" s="24"/>
+      <c r="N119" s="25"/>
+      <c r="O119" s="26"/>
+      <c r="P119" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q119" s="27"/>
     </row>
     <row r="120" ht="41.75">
       <c r="A120" s="23" t="s">
@@ -8611,17 +8619,17 @@
         <v>417</v>
       </c>
       <c r="L120" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M120" s="23">
         <v>0</v>
       </c>
-      <c r="N120" s="23"/>
-      <c r="O120" s="25"/>
-      <c r="P120" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q120" s="24"/>
+      <c r="N120" s="25"/>
+      <c r="O120" s="26"/>
+      <c r="P120" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q120" s="27"/>
     </row>
     <row r="121" ht="41.75">
       <c r="A121" s="23" t="s">
@@ -8658,17 +8666,17 @@
         <v>420</v>
       </c>
       <c r="L121" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M121" s="23">
         <v>0</v>
       </c>
-      <c r="N121" s="23"/>
-      <c r="O121" s="25"/>
-      <c r="P121" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q121" s="24"/>
+      <c r="N121" s="25"/>
+      <c r="O121" s="26"/>
+      <c r="P121" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q121" s="27"/>
     </row>
     <row r="122" ht="41.75">
       <c r="A122" s="23" t="s">
@@ -8705,17 +8713,17 @@
         <v>423</v>
       </c>
       <c r="L122" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M122" s="23">
         <v>0</v>
       </c>
-      <c r="N122" s="23"/>
-      <c r="O122" s="25"/>
-      <c r="P122" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q122" s="24"/>
+      <c r="N122" s="25"/>
+      <c r="O122" s="26"/>
+      <c r="P122" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q122" s="27"/>
     </row>
     <row r="123" ht="41.75">
       <c r="A123" s="23" t="s">
@@ -8752,17 +8760,17 @@
         <v>426</v>
       </c>
       <c r="L123" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M123" s="23">
         <v>0</v>
       </c>
-      <c r="N123" s="23"/>
-      <c r="O123" s="25"/>
-      <c r="P123" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q123" s="24"/>
+      <c r="N123" s="25"/>
+      <c r="O123" s="26"/>
+      <c r="P123" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q123" s="27"/>
     </row>
     <row r="124" ht="41.75">
       <c r="A124" s="23" t="s">
@@ -8799,17 +8807,17 @@
         <v>429</v>
       </c>
       <c r="L124" s="23" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="M124" s="23">
         <v>0</v>
       </c>
-      <c r="N124" s="23"/>
-      <c r="O124" s="25"/>
-      <c r="P124" s="24" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q124" s="24"/>
+      <c r="N124" s="25"/>
+      <c r="O124" s="26"/>
+      <c r="P124" s="27" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q124" s="27"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
@@ -8823,7 +8831,7 @@
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{78C0D931-6437-407d-A8EE-F0AAD7539E65}">
       <x14:conditionalFormattings>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="2" aboveAverage="0" operator="containsText" rank="0" text="Completed" id="{9900F14E-E88E-4678-B37F-D2B18A80BDCB}">
+          <x14:cfRule type="containsText" priority="2" aboveAverage="0" operator="containsText" rank="0" text="Completed" id="{FDC1F28B-DB5E-4B3E-8647-A744F5303491}">
             <xm:f>NOT(ISERROR(SEARCH("Completed",L2)))</xm:f>
             <x14:dxf>
               <font>
@@ -8841,7 +8849,7 @@
           <xm:sqref>L2:L124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="3" aboveAverage="0" operator="containsText" rank="0" text="In Progress" id="{328A7771-2D67-4AF9-927B-F5168AEDC497}">
+          <x14:cfRule type="containsText" priority="3" aboveAverage="0" operator="containsText" rank="0" text="In Progress" id="{887E5038-7C7F-47FB-B5D3-13002A47DF37}">
             <xm:f>NOT(ISERROR(SEARCH("In Progress",L2)))</xm:f>
             <x14:dxf>
               <font>
@@ -8858,7 +8866,7 @@
           <xm:sqref>L2:L124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="containsText" priority="4" aboveAverage="0" operator="containsText" rank="0" text="Revisit" id="{D95E3601-8BBD-4AC2-8690-F9252B36512B}">
+          <x14:cfRule type="containsText" priority="4" aboveAverage="0" operator="containsText" rank="0" text="Revisit" id="{846BE4B2-9D99-4613-9401-789B4563BFE1}">
             <xm:f>NOT(ISERROR(SEARCH("Revisit",L2)))</xm:f>
             <x14:dxf>
               <font>
@@ -8875,7 +8883,7 @@
           <xm:sqref>L2:L124</xm:sqref>
         </x14:conditionalFormatting>
         <x14:conditionalFormatting xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main">
-          <x14:cfRule type="dataBar" priority="5" id="{6FE29B43-BA9E-4E25-B324-55E9B9B9FD66}">
+          <x14:cfRule type="dataBar" priority="5" id="{54F7ED55-7419-4692-B846-C205F6A90E1D}">
             <x14:dataBar maxLength="90" minLength="10" axisPosition="automatic" direction="context">
               <x14:cfvo type="min"/>
               <x14:cfvo type="max"/>
@@ -8890,7 +8898,7 @@
     </ext>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{776AAC6B-FEEC-4395-82D3-88E03D01DF9B}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{AE043924-AEDC-4236-995A-FAA43BCEA317}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"☐ Not Started,◐ In Progress,☑ Completed,↻ Revisit"</xm:f>
           </x14:formula1>
@@ -8899,7 +8907,7 @@
           </x14:formula2>
           <xm:sqref>L2:L124</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{60F40BE6-F493-4A59-A361-5A88D59FABA0}" type="whole" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{7AD7C140-7B24-4CA6-BDC5-F8DBA0E86D39}" type="whole" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>
@@ -8932,312 +8940,312 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>435</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
     </row>
     <row r="3" ht="15">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="29" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="29" t="s">
         <v>436</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="29" t="s">
         <v>437</v>
       </c>
-      <c r="D3" s="27" t="s">
+      <c r="D3" s="29" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="27" t="s">
+      <c r="E3" s="29" t="s">
         <v>31</v>
       </c>
-      <c r="F3" s="27" t="s">
+      <c r="F3" s="29" t="s">
         <v>438</v>
       </c>
-      <c r="G3" s="27" t="s">
+      <c r="G3" s="29" t="s">
         <v>439</v>
       </c>
     </row>
     <row r="4" ht="23.850000000000001">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="29" t="s">
         <v>12</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="29" t="s">
         <v>42</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="29" t="s">
         <v>440</v>
       </c>
-      <c r="D4" s="27">
+      <c r="D4" s="29">
         <v>10</v>
       </c>
-      <c r="E4" s="27">
+      <c r="E4" s="29">
         <v>20</v>
       </c>
-      <c r="F4" s="27">
+      <c r="F4" s="29">
         <v>3</v>
       </c>
-      <c r="G4" s="27" t="s">
+      <c r="G4" s="29" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="5" ht="23.850000000000001">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="29" t="s">
         <v>14</v>
       </c>
-      <c r="B5" s="27" t="s">
+      <c r="B5" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="C5" s="27" t="s">
+      <c r="C5" s="29" t="s">
         <v>442</v>
       </c>
-      <c r="D5" s="27">
+      <c r="D5" s="29">
         <v>12</v>
       </c>
-      <c r="E5" s="27">
+      <c r="E5" s="29">
         <v>36</v>
       </c>
-      <c r="F5" s="27">
+      <c r="F5" s="29">
         <v>5</v>
       </c>
-      <c r="G5" s="27" t="s">
+      <c r="G5" s="29" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="6" ht="23.850000000000001">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="29" t="s">
         <v>15</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="29" t="s">
         <v>118</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="29" t="s">
         <v>443</v>
       </c>
-      <c r="D6" s="27">
+      <c r="D6" s="29">
         <v>12</v>
       </c>
-      <c r="E6" s="27">
+      <c r="E6" s="29">
         <v>36</v>
       </c>
-      <c r="F6" s="27">
+      <c r="F6" s="29">
         <v>5</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="G6" s="29" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="7" ht="23.850000000000001">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="29" t="s">
         <v>16</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="29" t="s">
         <v>444</v>
       </c>
-      <c r="D7" s="27">
+      <c r="D7" s="29">
         <v>14</v>
       </c>
-      <c r="E7" s="27">
+      <c r="E7" s="29">
         <v>56</v>
       </c>
-      <c r="F7" s="27">
+      <c r="F7" s="29">
         <v>7</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="29" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="8" ht="23.850000000000001">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="29" t="s">
         <v>17</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="29" t="s">
         <v>199</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="29" t="s">
         <v>445</v>
       </c>
-      <c r="D8" s="27">
+      <c r="D8" s="29">
         <v>8</v>
       </c>
-      <c r="E8" s="27">
+      <c r="E8" s="29">
         <v>32</v>
       </c>
-      <c r="F8" s="27">
+      <c r="F8" s="29">
         <v>4</v>
       </c>
-      <c r="G8" s="27" t="s">
+      <c r="G8" s="29" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="9" ht="23.850000000000001">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="29" t="s">
         <v>18</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="29" t="s">
         <v>226</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="29" t="s">
         <v>447</v>
       </c>
-      <c r="D9" s="27">
+      <c r="D9" s="29">
         <v>12</v>
       </c>
-      <c r="E9" s="27">
-        <v>48</v>
-      </c>
-      <c r="F9" s="27">
+      <c r="E9" s="29">
+        <v>48</v>
+      </c>
+      <c r="F9" s="29">
         <v>6</v>
       </c>
-      <c r="G9" s="27" t="s">
+      <c r="G9" s="29" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="10" ht="23.850000000000001">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="29" t="s">
         <v>19</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="29" t="s">
         <v>263</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="29" t="s">
         <v>448</v>
       </c>
-      <c r="D10" s="27">
+      <c r="D10" s="29">
         <v>9</v>
       </c>
-      <c r="E10" s="27">
+      <c r="E10" s="29">
         <v>36</v>
       </c>
-      <c r="F10" s="27">
+      <c r="F10" s="29">
         <v>5</v>
       </c>
-      <c r="G10" s="27" t="s">
+      <c r="G10" s="29" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="11" ht="23.850000000000001">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="29" t="s">
         <v>20</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="29" t="s">
         <v>291</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="29" t="s">
         <v>449</v>
       </c>
-      <c r="D11" s="27">
+      <c r="D11" s="29">
         <v>10</v>
       </c>
-      <c r="E11" s="27">
+      <c r="E11" s="29">
         <v>40</v>
       </c>
-      <c r="F11" s="27">
+      <c r="F11" s="29">
         <v>5</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="29" t="s">
         <v>446</v>
       </c>
     </row>
     <row r="12" ht="23.850000000000001">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="29" t="s">
         <v>21</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="29" t="s">
         <v>322</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="29" t="s">
         <v>450</v>
       </c>
-      <c r="D12" s="27">
+      <c r="D12" s="29">
         <v>9</v>
       </c>
-      <c r="E12" s="27">
+      <c r="E12" s="29">
         <v>36</v>
       </c>
-      <c r="F12" s="27">
+      <c r="F12" s="29">
         <v>5</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="29" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="13" ht="23.850000000000001">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="29" t="s">
         <v>22</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="29" t="s">
         <v>350</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="29" t="s">
         <v>451</v>
       </c>
-      <c r="D13" s="27">
+      <c r="D13" s="29">
         <v>7</v>
       </c>
-      <c r="E13" s="27">
+      <c r="E13" s="29">
         <v>28</v>
       </c>
-      <c r="F13" s="27">
+      <c r="F13" s="29">
         <v>4</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="29" t="s">
         <v>441</v>
       </c>
     </row>
     <row r="14" ht="23.850000000000001">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="29" t="s">
         <v>23</v>
       </c>
-      <c r="B14" s="27" t="s">
+      <c r="B14" s="29" t="s">
         <v>372</v>
       </c>
-      <c r="C14" s="27" t="s">
+      <c r="C14" s="29" t="s">
         <v>452</v>
       </c>
-      <c r="D14" s="27">
+      <c r="D14" s="29">
         <v>10</v>
       </c>
-      <c r="E14" s="27">
+      <c r="E14" s="29">
         <v>40</v>
       </c>
-      <c r="F14" s="27">
+      <c r="F14" s="29">
         <v>5</v>
       </c>
-      <c r="G14" s="27" t="s">
+      <c r="G14" s="29" t="s">
         <v>453</v>
       </c>
     </row>
     <row r="15" ht="23.850000000000001">
-      <c r="A15" s="27" t="s">
+      <c r="A15" s="29" t="s">
         <v>24</v>
       </c>
-      <c r="B15" s="27" t="s">
+      <c r="B15" s="29" t="s">
         <v>404</v>
       </c>
-      <c r="C15" s="27" t="s">
+      <c r="C15" s="29" t="s">
         <v>454</v>
       </c>
-      <c r="D15" s="27">
+      <c r="D15" s="29">
         <v>10</v>
       </c>
-      <c r="E15" s="27">
+      <c r="E15" s="29">
         <v>80</v>
       </c>
-      <c r="F15" s="27">
+      <c r="F15" s="29">
         <v>10</v>
       </c>
-      <c r="G15" s="27" t="s">
+      <c r="G15" s="29" t="s">
         <v>441</v>
       </c>
     </row>
@@ -9269,16 +9277,16 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>455</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
-      <c r="G1" s="26"/>
-      <c r="H1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
     </row>
     <row r="3" ht="15">
       <c r="A3" s="1" t="s">
@@ -9313,20 +9321,20 @@
       <c r="B4" s="1" t="s">
         <v>464</v>
       </c>
-      <c r="C4" s="28"/>
-      <c r="D4" s="29">
-        <v>0</v>
-      </c>
-      <c r="E4" s="29">
-        <v>0</v>
-      </c>
-      <c r="F4" s="29">
-        <v>0</v>
-      </c>
-      <c r="G4" s="29">
-        <v>0</v>
-      </c>
-      <c r="H4" s="29">
+      <c r="C4" s="30"/>
+      <c r="D4" s="31">
+        <v>0</v>
+      </c>
+      <c r="E4" s="31">
+        <v>0</v>
+      </c>
+      <c r="F4" s="31">
+        <v>0</v>
+      </c>
+      <c r="G4" s="31">
+        <v>0</v>
+      </c>
+      <c r="H4" s="31">
         <f t="shared" ref="H4:H9" si="1">AVERAGE(D4:G4)</f>
         <v>0</v>
       </c>
@@ -9338,20 +9346,20 @@
       <c r="B5" s="1" t="s">
         <v>465</v>
       </c>
-      <c r="C5" s="28"/>
-      <c r="D5" s="29">
-        <v>0</v>
-      </c>
-      <c r="E5" s="29">
-        <v>0</v>
-      </c>
-      <c r="F5" s="29">
-        <v>0</v>
-      </c>
-      <c r="G5" s="29">
-        <v>0</v>
-      </c>
-      <c r="H5" s="29">
+      <c r="C5" s="30"/>
+      <c r="D5" s="31">
+        <v>0</v>
+      </c>
+      <c r="E5" s="31">
+        <v>0</v>
+      </c>
+      <c r="F5" s="31">
+        <v>0</v>
+      </c>
+      <c r="G5" s="31">
+        <v>0</v>
+      </c>
+      <c r="H5" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9363,20 +9371,20 @@
       <c r="B6" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="C6" s="28"/>
-      <c r="D6" s="29">
-        <v>0</v>
-      </c>
-      <c r="E6" s="29">
-        <v>0</v>
-      </c>
-      <c r="F6" s="29">
-        <v>0</v>
-      </c>
-      <c r="G6" s="29">
-        <v>0</v>
-      </c>
-      <c r="H6" s="29">
+      <c r="C6" s="30"/>
+      <c r="D6" s="31">
+        <v>0</v>
+      </c>
+      <c r="E6" s="31">
+        <v>0</v>
+      </c>
+      <c r="F6" s="31">
+        <v>0</v>
+      </c>
+      <c r="G6" s="31">
+        <v>0</v>
+      </c>
+      <c r="H6" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9388,20 +9396,20 @@
       <c r="B7" s="1" t="s">
         <v>467</v>
       </c>
-      <c r="C7" s="28"/>
-      <c r="D7" s="29">
-        <v>0</v>
-      </c>
-      <c r="E7" s="29">
-        <v>0</v>
-      </c>
-      <c r="F7" s="29">
-        <v>0</v>
-      </c>
-      <c r="G7" s="29">
-        <v>0</v>
-      </c>
-      <c r="H7" s="29">
+      <c r="C7" s="30"/>
+      <c r="D7" s="31">
+        <v>0</v>
+      </c>
+      <c r="E7" s="31">
+        <v>0</v>
+      </c>
+      <c r="F7" s="31">
+        <v>0</v>
+      </c>
+      <c r="G7" s="31">
+        <v>0</v>
+      </c>
+      <c r="H7" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9413,20 +9421,20 @@
       <c r="B8" s="1" t="s">
         <v>468</v>
       </c>
-      <c r="C8" s="28"/>
-      <c r="D8" s="29">
-        <v>0</v>
-      </c>
-      <c r="E8" s="29">
-        <v>0</v>
-      </c>
-      <c r="F8" s="29">
-        <v>0</v>
-      </c>
-      <c r="G8" s="29">
-        <v>0</v>
-      </c>
-      <c r="H8" s="29">
+      <c r="C8" s="30"/>
+      <c r="D8" s="31">
+        <v>0</v>
+      </c>
+      <c r="E8" s="31">
+        <v>0</v>
+      </c>
+      <c r="F8" s="31">
+        <v>0</v>
+      </c>
+      <c r="G8" s="31">
+        <v>0</v>
+      </c>
+      <c r="H8" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9438,20 +9446,20 @@
       <c r="B9" s="1" t="s">
         <v>469</v>
       </c>
-      <c r="C9" s="28"/>
-      <c r="D9" s="29">
-        <v>0</v>
-      </c>
-      <c r="E9" s="29">
-        <v>0</v>
-      </c>
-      <c r="F9" s="29">
-        <v>0</v>
-      </c>
-      <c r="G9" s="29">
-        <v>0</v>
-      </c>
-      <c r="H9" s="29">
+      <c r="C9" s="30"/>
+      <c r="D9" s="31">
+        <v>0</v>
+      </c>
+      <c r="E9" s="31">
+        <v>0</v>
+      </c>
+      <c r="F9" s="31">
+        <v>0</v>
+      </c>
+      <c r="G9" s="31">
+        <v>0</v>
+      </c>
+      <c r="H9" s="31">
         <f t="shared" si="1"/>
         <v>0</v>
       </c>
@@ -9463,20 +9471,20 @@
       <c r="B10" s="1" t="s">
         <v>470</v>
       </c>
-      <c r="C10" s="28"/>
-      <c r="D10" s="29">
-        <v>0</v>
-      </c>
-      <c r="E10" s="29">
-        <v>0</v>
-      </c>
-      <c r="F10" s="29">
-        <v>0</v>
-      </c>
-      <c r="G10" s="29">
-        <v>0</v>
-      </c>
-      <c r="H10" s="29">
+      <c r="C10" s="30"/>
+      <c r="D10" s="31">
+        <v>0</v>
+      </c>
+      <c r="E10" s="31">
+        <v>0</v>
+      </c>
+      <c r="F10" s="31">
+        <v>0</v>
+      </c>
+      <c r="G10" s="31">
+        <v>0</v>
+      </c>
+      <c r="H10" s="31">
         <f t="shared" ref="H10:H11" si="2">AVERAGE(D10:G10)</f>
         <v>0</v>
       </c>
@@ -9488,35 +9496,35 @@
       <c r="B11" s="1" t="s">
         <v>471</v>
       </c>
-      <c r="C11" s="28"/>
-      <c r="D11" s="29">
-        <v>0</v>
-      </c>
-      <c r="E11" s="29">
-        <v>0</v>
-      </c>
-      <c r="F11" s="29">
-        <v>0</v>
-      </c>
-      <c r="G11" s="29">
-        <v>0</v>
-      </c>
-      <c r="H11" s="29">
+      <c r="C11" s="30"/>
+      <c r="D11" s="31">
+        <v>0</v>
+      </c>
+      <c r="E11" s="31">
+        <v>0</v>
+      </c>
+      <c r="F11" s="31">
+        <v>0</v>
+      </c>
+      <c r="G11" s="31">
+        <v>0</v>
+      </c>
+      <c r="H11" s="31">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
     </row>
     <row r="14" ht="15" customHeight="1">
-      <c r="A14" s="30" t="s">
+      <c r="A14" s="32" t="s">
         <v>472</v>
       </c>
-      <c r="B14" s="30"/>
-      <c r="C14" s="30"/>
-      <c r="D14" s="30"/>
-      <c r="E14" s="30"/>
-      <c r="F14" s="30"/>
-      <c r="G14" s="30"/>
-      <c r="H14" s="30"/>
+      <c r="B14" s="32"/>
+      <c r="C14" s="32"/>
+      <c r="D14" s="32"/>
+      <c r="E14" s="32"/>
+      <c r="F14" s="32"/>
+      <c r="G14" s="32"/>
+      <c r="H14" s="32"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -9545,7 +9553,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="1" disablePrompts="0">
-        <x14:dataValidation xr:uid="{A308CF30-536E-4B1F-BF91-43B0354036A4}" type="decimal" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{17290064-D856-4AF2-8A10-7CC518FD38C5}" type="decimal" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>0</xm:f>
           </x14:formula1>
@@ -9606,1404 +9614,1404 @@
       </c>
     </row>
     <row r="2" ht="15">
-      <c r="A2" s="28"/>
+      <c r="A2" s="30"/>
       <c r="D2" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J2" s="28"/>
+      <c r="J2" s="30"/>
     </row>
     <row r="3" ht="15">
-      <c r="A3" s="28"/>
+      <c r="A3" s="30"/>
       <c r="D3" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J3" s="28"/>
+      <c r="J3" s="30"/>
     </row>
     <row r="4" ht="15">
-      <c r="A4" s="28"/>
+      <c r="A4" s="30"/>
       <c r="D4" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J4" s="28"/>
+      <c r="J4" s="30"/>
     </row>
     <row r="5" ht="15">
-      <c r="A5" s="28"/>
+      <c r="A5" s="30"/>
       <c r="D5" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J5" s="28"/>
+      <c r="J5" s="30"/>
     </row>
     <row r="6" ht="15">
-      <c r="A6" s="28"/>
+      <c r="A6" s="30"/>
       <c r="D6" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J6" s="28"/>
+      <c r="J6" s="30"/>
     </row>
     <row r="7" ht="15">
-      <c r="A7" s="28"/>
+      <c r="A7" s="30"/>
       <c r="D7" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J7" s="28"/>
+      <c r="J7" s="30"/>
     </row>
     <row r="8" ht="15">
-      <c r="A8" s="28"/>
+      <c r="A8" s="30"/>
       <c r="D8" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J8" s="28"/>
+      <c r="J8" s="30"/>
     </row>
     <row r="9" ht="15">
-      <c r="A9" s="28"/>
+      <c r="A9" s="30"/>
       <c r="D9" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J9" s="28"/>
+      <c r="J9" s="30"/>
     </row>
     <row r="10" ht="15">
-      <c r="A10" s="28"/>
+      <c r="A10" s="30"/>
       <c r="D10" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J10" s="28"/>
+      <c r="J10" s="30"/>
     </row>
     <row r="11" ht="15">
-      <c r="A11" s="28"/>
+      <c r="A11" s="30"/>
       <c r="D11" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J11" s="28"/>
+      <c r="J11" s="30"/>
     </row>
     <row r="12" ht="15">
-      <c r="A12" s="28"/>
+      <c r="A12" s="30"/>
       <c r="D12" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J12" s="28"/>
+      <c r="J12" s="30"/>
     </row>
     <row r="13" ht="15">
-      <c r="A13" s="28"/>
+      <c r="A13" s="30"/>
       <c r="D13" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J13" s="28"/>
+      <c r="J13" s="30"/>
     </row>
     <row r="14" ht="15">
-      <c r="A14" s="28"/>
+      <c r="A14" s="30"/>
       <c r="D14" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J14" s="28"/>
+      <c r="J14" s="30"/>
     </row>
     <row r="15" ht="15">
-      <c r="A15" s="28"/>
+      <c r="A15" s="30"/>
       <c r="D15" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J15" s="28"/>
+      <c r="J15" s="30"/>
     </row>
     <row r="16" ht="15">
-      <c r="A16" s="28"/>
+      <c r="A16" s="30"/>
       <c r="D16" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J16" s="28"/>
+      <c r="J16" s="30"/>
     </row>
     <row r="17" ht="15">
-      <c r="A17" s="28"/>
+      <c r="A17" s="30"/>
       <c r="D17" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J17" s="28"/>
+      <c r="J17" s="30"/>
     </row>
     <row r="18" ht="15">
-      <c r="A18" s="28"/>
+      <c r="A18" s="30"/>
       <c r="D18" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J18" s="28"/>
+      <c r="J18" s="30"/>
     </row>
     <row r="19" ht="15">
-      <c r="A19" s="28"/>
+      <c r="A19" s="30"/>
       <c r="D19" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J19" s="28"/>
+      <c r="J19" s="30"/>
     </row>
     <row r="20" ht="15">
-      <c r="A20" s="28"/>
+      <c r="A20" s="30"/>
       <c r="D20" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J20" s="28"/>
+      <c r="J20" s="30"/>
     </row>
     <row r="21" ht="15">
-      <c r="A21" s="28"/>
+      <c r="A21" s="30"/>
       <c r="D21" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J21" s="28"/>
+      <c r="J21" s="30"/>
     </row>
     <row r="22" ht="15">
-      <c r="A22" s="28"/>
+      <c r="A22" s="30"/>
       <c r="D22" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J22" s="28"/>
+      <c r="J22" s="30"/>
     </row>
     <row r="23" ht="15">
-      <c r="A23" s="28"/>
+      <c r="A23" s="30"/>
       <c r="D23" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J23" s="28"/>
+      <c r="J23" s="30"/>
     </row>
     <row r="24" ht="15">
-      <c r="A24" s="28"/>
+      <c r="A24" s="30"/>
       <c r="D24" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J24" s="28"/>
+      <c r="J24" s="30"/>
     </row>
     <row r="25" ht="15">
-      <c r="A25" s="28"/>
+      <c r="A25" s="30"/>
       <c r="D25" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J25" s="28"/>
+      <c r="J25" s="30"/>
     </row>
     <row r="26" ht="15">
-      <c r="A26" s="28"/>
+      <c r="A26" s="30"/>
       <c r="D26" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J26" s="28"/>
+      <c r="J26" s="30"/>
     </row>
     <row r="27" ht="15">
-      <c r="A27" s="28"/>
+      <c r="A27" s="30"/>
       <c r="D27" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J27" s="28"/>
+      <c r="J27" s="30"/>
     </row>
     <row r="28" ht="15">
-      <c r="A28" s="28"/>
+      <c r="A28" s="30"/>
       <c r="D28" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J28" s="28"/>
+      <c r="J28" s="30"/>
     </row>
     <row r="29" ht="15">
-      <c r="A29" s="28"/>
+      <c r="A29" s="30"/>
       <c r="D29" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J29" s="28"/>
+      <c r="J29" s="30"/>
     </row>
     <row r="30" ht="15">
-      <c r="A30" s="28"/>
+      <c r="A30" s="30"/>
       <c r="D30" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J30" s="28"/>
+      <c r="J30" s="30"/>
     </row>
     <row r="31" ht="15">
-      <c r="A31" s="28"/>
+      <c r="A31" s="30"/>
       <c r="D31" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J31" s="28"/>
+      <c r="J31" s="30"/>
     </row>
     <row r="32" ht="15">
-      <c r="A32" s="28"/>
+      <c r="A32" s="30"/>
       <c r="D32" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J32" s="28"/>
+      <c r="J32" s="30"/>
     </row>
     <row r="33" ht="15">
-      <c r="A33" s="28"/>
+      <c r="A33" s="30"/>
       <c r="D33" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J33" s="28"/>
+      <c r="J33" s="30"/>
     </row>
     <row r="34" ht="15">
-      <c r="A34" s="28"/>
+      <c r="A34" s="30"/>
       <c r="D34" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J34" s="28"/>
+      <c r="J34" s="30"/>
     </row>
     <row r="35" ht="15">
-      <c r="A35" s="28"/>
+      <c r="A35" s="30"/>
       <c r="D35" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J35" s="28"/>
+      <c r="J35" s="30"/>
     </row>
     <row r="36" ht="15">
-      <c r="A36" s="28"/>
+      <c r="A36" s="30"/>
       <c r="D36" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J36" s="28"/>
+      <c r="J36" s="30"/>
     </row>
     <row r="37" ht="15">
-      <c r="A37" s="28"/>
+      <c r="A37" s="30"/>
       <c r="D37" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J37" s="28"/>
+      <c r="J37" s="30"/>
     </row>
     <row r="38" ht="15">
-      <c r="A38" s="28"/>
+      <c r="A38" s="30"/>
       <c r="D38" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J38" s="28"/>
+      <c r="J38" s="30"/>
     </row>
     <row r="39" ht="15">
-      <c r="A39" s="28"/>
+      <c r="A39" s="30"/>
       <c r="D39" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J39" s="28"/>
+      <c r="J39" s="30"/>
     </row>
     <row r="40" ht="15">
-      <c r="A40" s="28"/>
+      <c r="A40" s="30"/>
       <c r="D40" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J40" s="28"/>
+      <c r="J40" s="30"/>
     </row>
     <row r="41" ht="15">
-      <c r="A41" s="28"/>
+      <c r="A41" s="30"/>
       <c r="D41" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J41" s="28"/>
+      <c r="J41" s="30"/>
     </row>
     <row r="42" ht="15">
-      <c r="A42" s="28"/>
+      <c r="A42" s="30"/>
       <c r="D42" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J42" s="28"/>
+      <c r="J42" s="30"/>
     </row>
     <row r="43" ht="15">
-      <c r="A43" s="28"/>
+      <c r="A43" s="30"/>
       <c r="D43" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J43" s="28"/>
+      <c r="J43" s="30"/>
     </row>
     <row r="44" ht="15">
-      <c r="A44" s="28"/>
+      <c r="A44" s="30"/>
       <c r="D44" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J44" s="28"/>
+      <c r="J44" s="30"/>
     </row>
     <row r="45" ht="15">
-      <c r="A45" s="28"/>
+      <c r="A45" s="30"/>
       <c r="D45" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J45" s="28"/>
+      <c r="J45" s="30"/>
     </row>
     <row r="46" ht="15">
-      <c r="A46" s="28"/>
+      <c r="A46" s="30"/>
       <c r="D46" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J46" s="28"/>
+      <c r="J46" s="30"/>
     </row>
     <row r="47" ht="15">
-      <c r="A47" s="28"/>
+      <c r="A47" s="30"/>
       <c r="D47" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J47" s="28"/>
+      <c r="J47" s="30"/>
     </row>
     <row r="48" ht="15">
-      <c r="A48" s="28"/>
+      <c r="A48" s="30"/>
       <c r="D48" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J48" s="28"/>
+      <c r="J48" s="30"/>
     </row>
     <row r="49" ht="15">
-      <c r="A49" s="28"/>
+      <c r="A49" s="30"/>
       <c r="D49" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J49" s="28"/>
+      <c r="J49" s="30"/>
     </row>
     <row r="50" ht="15">
-      <c r="A50" s="28"/>
+      <c r="A50" s="30"/>
       <c r="D50" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J50" s="28"/>
+      <c r="J50" s="30"/>
     </row>
     <row r="51" ht="15">
-      <c r="A51" s="28"/>
+      <c r="A51" s="30"/>
       <c r="D51" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J51" s="28"/>
+      <c r="J51" s="30"/>
     </row>
     <row r="52" ht="15">
-      <c r="A52" s="28"/>
+      <c r="A52" s="30"/>
       <c r="D52" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J52" s="28"/>
+      <c r="J52" s="30"/>
     </row>
     <row r="53" ht="15">
-      <c r="A53" s="28"/>
+      <c r="A53" s="30"/>
       <c r="D53" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J53" s="28"/>
+      <c r="J53" s="30"/>
     </row>
     <row r="54" ht="15">
-      <c r="A54" s="28"/>
+      <c r="A54" s="30"/>
       <c r="D54" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J54" s="28"/>
+      <c r="J54" s="30"/>
     </row>
     <row r="55" ht="15">
-      <c r="A55" s="28"/>
+      <c r="A55" s="30"/>
       <c r="D55" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J55" s="28"/>
+      <c r="J55" s="30"/>
     </row>
     <row r="56" ht="15">
-      <c r="A56" s="28"/>
+      <c r="A56" s="30"/>
       <c r="D56" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J56" s="28"/>
+      <c r="J56" s="30"/>
     </row>
     <row r="57" ht="15">
-      <c r="A57" s="28"/>
+      <c r="A57" s="30"/>
       <c r="D57" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J57" s="28"/>
+      <c r="J57" s="30"/>
     </row>
     <row r="58" ht="15">
-      <c r="A58" s="28"/>
+      <c r="A58" s="30"/>
       <c r="D58" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J58" s="28"/>
+      <c r="J58" s="30"/>
     </row>
     <row r="59" ht="15">
-      <c r="A59" s="28"/>
+      <c r="A59" s="30"/>
       <c r="D59" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J59" s="28"/>
+      <c r="J59" s="30"/>
     </row>
     <row r="60" ht="15">
-      <c r="A60" s="28"/>
+      <c r="A60" s="30"/>
       <c r="D60" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J60" s="28"/>
+      <c r="J60" s="30"/>
     </row>
     <row r="61" ht="15">
-      <c r="A61" s="28"/>
+      <c r="A61" s="30"/>
       <c r="D61" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J61" s="28"/>
+      <c r="J61" s="30"/>
     </row>
     <row r="62" ht="15">
-      <c r="A62" s="28"/>
+      <c r="A62" s="30"/>
       <c r="D62" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J62" s="28"/>
+      <c r="J62" s="30"/>
     </row>
     <row r="63" ht="15">
-      <c r="A63" s="28"/>
+      <c r="A63" s="30"/>
       <c r="D63" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J63" s="28"/>
+      <c r="J63" s="30"/>
     </row>
     <row r="64" ht="15">
-      <c r="A64" s="28"/>
+      <c r="A64" s="30"/>
       <c r="D64" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J64" s="28"/>
+      <c r="J64" s="30"/>
     </row>
     <row r="65" ht="15">
-      <c r="A65" s="28"/>
+      <c r="A65" s="30"/>
       <c r="D65" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J65" s="28"/>
+      <c r="J65" s="30"/>
     </row>
     <row r="66" ht="15">
-      <c r="A66" s="28"/>
+      <c r="A66" s="30"/>
       <c r="D66" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J66" s="28"/>
+      <c r="J66" s="30"/>
     </row>
     <row r="67" ht="15">
-      <c r="A67" s="28"/>
+      <c r="A67" s="30"/>
       <c r="D67" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J67" s="28"/>
+      <c r="J67" s="30"/>
     </row>
     <row r="68" ht="15">
-      <c r="A68" s="28"/>
+      <c r="A68" s="30"/>
       <c r="D68" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J68" s="28"/>
+      <c r="J68" s="30"/>
     </row>
     <row r="69" ht="15">
-      <c r="A69" s="28"/>
+      <c r="A69" s="30"/>
       <c r="D69" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J69" s="28"/>
+      <c r="J69" s="30"/>
     </row>
     <row r="70" ht="15">
-      <c r="A70" s="28"/>
+      <c r="A70" s="30"/>
       <c r="D70" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J70" s="28"/>
+      <c r="J70" s="30"/>
     </row>
     <row r="71" ht="15">
-      <c r="A71" s="28"/>
+      <c r="A71" s="30"/>
       <c r="D71" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J71" s="28"/>
+      <c r="J71" s="30"/>
     </row>
     <row r="72" ht="15">
-      <c r="A72" s="28"/>
+      <c r="A72" s="30"/>
       <c r="D72" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J72" s="28"/>
+      <c r="J72" s="30"/>
     </row>
     <row r="73" ht="15">
-      <c r="A73" s="28"/>
+      <c r="A73" s="30"/>
       <c r="D73" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J73" s="28"/>
+      <c r="J73" s="30"/>
     </row>
     <row r="74" ht="15">
-      <c r="A74" s="28"/>
+      <c r="A74" s="30"/>
       <c r="D74" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J74" s="28"/>
+      <c r="J74" s="30"/>
     </row>
     <row r="75" ht="15">
-      <c r="A75" s="28"/>
+      <c r="A75" s="30"/>
       <c r="D75" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J75" s="28"/>
+      <c r="J75" s="30"/>
     </row>
     <row r="76" ht="15">
-      <c r="A76" s="28"/>
+      <c r="A76" s="30"/>
       <c r="D76" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J76" s="28"/>
+      <c r="J76" s="30"/>
     </row>
     <row r="77" ht="15">
-      <c r="A77" s="28"/>
+      <c r="A77" s="30"/>
       <c r="D77" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J77" s="28"/>
+      <c r="J77" s="30"/>
     </row>
     <row r="78" ht="15">
-      <c r="A78" s="28"/>
+      <c r="A78" s="30"/>
       <c r="D78" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J78" s="28"/>
+      <c r="J78" s="30"/>
     </row>
     <row r="79" ht="15">
-      <c r="A79" s="28"/>
+      <c r="A79" s="30"/>
       <c r="D79" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J79" s="28"/>
+      <c r="J79" s="30"/>
     </row>
     <row r="80" ht="15">
-      <c r="A80" s="28"/>
+      <c r="A80" s="30"/>
       <c r="D80" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J80" s="28"/>
+      <c r="J80" s="30"/>
     </row>
     <row r="81" ht="15">
-      <c r="A81" s="28"/>
+      <c r="A81" s="30"/>
       <c r="D81" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J81" s="28"/>
+      <c r="J81" s="30"/>
     </row>
     <row r="82" ht="15">
-      <c r="A82" s="28"/>
+      <c r="A82" s="30"/>
       <c r="D82" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J82" s="28"/>
+      <c r="J82" s="30"/>
     </row>
     <row r="83" ht="15">
-      <c r="A83" s="28"/>
+      <c r="A83" s="30"/>
       <c r="D83" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J83" s="28"/>
+      <c r="J83" s="30"/>
     </row>
     <row r="84" ht="15">
-      <c r="A84" s="28"/>
+      <c r="A84" s="30"/>
       <c r="D84" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J84" s="28"/>
+      <c r="J84" s="30"/>
     </row>
     <row r="85" ht="15">
-      <c r="A85" s="28"/>
+      <c r="A85" s="30"/>
       <c r="D85" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J85" s="28"/>
+      <c r="J85" s="30"/>
     </row>
     <row r="86" ht="15">
-      <c r="A86" s="28"/>
+      <c r="A86" s="30"/>
       <c r="D86" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J86" s="28"/>
+      <c r="J86" s="30"/>
     </row>
     <row r="87" ht="15">
-      <c r="A87" s="28"/>
+      <c r="A87" s="30"/>
       <c r="D87" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J87" s="28"/>
+      <c r="J87" s="30"/>
     </row>
     <row r="88" ht="15">
-      <c r="A88" s="28"/>
+      <c r="A88" s="30"/>
       <c r="D88" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J88" s="28"/>
+      <c r="J88" s="30"/>
     </row>
     <row r="89" ht="15">
-      <c r="A89" s="28"/>
+      <c r="A89" s="30"/>
       <c r="D89" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J89" s="28"/>
+      <c r="J89" s="30"/>
     </row>
     <row r="90" ht="15">
-      <c r="A90" s="28"/>
+      <c r="A90" s="30"/>
       <c r="D90" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J90" s="28"/>
+      <c r="J90" s="30"/>
     </row>
     <row r="91" ht="15">
-      <c r="A91" s="28"/>
+      <c r="A91" s="30"/>
       <c r="D91" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J91" s="28"/>
+      <c r="J91" s="30"/>
     </row>
     <row r="92" ht="15">
-      <c r="A92" s="28"/>
+      <c r="A92" s="30"/>
       <c r="D92" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J92" s="28"/>
+      <c r="J92" s="30"/>
     </row>
     <row r="93" ht="15">
-      <c r="A93" s="28"/>
+      <c r="A93" s="30"/>
       <c r="D93" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J93" s="28"/>
+      <c r="J93" s="30"/>
     </row>
     <row r="94" ht="15">
-      <c r="A94" s="28"/>
+      <c r="A94" s="30"/>
       <c r="D94" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J94" s="28"/>
+      <c r="J94" s="30"/>
     </row>
     <row r="95" ht="15">
-      <c r="A95" s="28"/>
+      <c r="A95" s="30"/>
       <c r="D95" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J95" s="28"/>
+      <c r="J95" s="30"/>
     </row>
     <row r="96" ht="15">
-      <c r="A96" s="28"/>
+      <c r="A96" s="30"/>
       <c r="D96" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J96" s="28"/>
+      <c r="J96" s="30"/>
     </row>
     <row r="97" ht="15">
-      <c r="A97" s="28"/>
+      <c r="A97" s="30"/>
       <c r="D97" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J97" s="28"/>
+      <c r="J97" s="30"/>
     </row>
     <row r="98" ht="15">
-      <c r="A98" s="28"/>
+      <c r="A98" s="30"/>
       <c r="D98" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J98" s="28"/>
+      <c r="J98" s="30"/>
     </row>
     <row r="99" ht="15">
-      <c r="A99" s="28"/>
+      <c r="A99" s="30"/>
       <c r="D99" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J99" s="28"/>
+      <c r="J99" s="30"/>
     </row>
     <row r="100" ht="15">
-      <c r="A100" s="28"/>
+      <c r="A100" s="30"/>
       <c r="D100" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J100" s="28"/>
+      <c r="J100" s="30"/>
     </row>
     <row r="101" ht="15">
-      <c r="A101" s="28"/>
+      <c r="A101" s="30"/>
       <c r="D101" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J101" s="28"/>
+      <c r="J101" s="30"/>
     </row>
     <row r="102" ht="15">
-      <c r="A102" s="28"/>
+      <c r="A102" s="30"/>
       <c r="D102" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J102" s="28"/>
+      <c r="J102" s="30"/>
     </row>
     <row r="103" ht="15">
-      <c r="A103" s="28"/>
+      <c r="A103" s="30"/>
       <c r="D103" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J103" s="28"/>
+      <c r="J103" s="30"/>
     </row>
     <row r="104" ht="15">
-      <c r="A104" s="28"/>
+      <c r="A104" s="30"/>
       <c r="D104" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J104" s="28"/>
+      <c r="J104" s="30"/>
     </row>
     <row r="105" ht="15">
-      <c r="A105" s="28"/>
+      <c r="A105" s="30"/>
       <c r="D105" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J105" s="28"/>
+      <c r="J105" s="30"/>
     </row>
     <row r="106" ht="15">
-      <c r="A106" s="28"/>
+      <c r="A106" s="30"/>
       <c r="D106" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J106" s="28"/>
+      <c r="J106" s="30"/>
     </row>
     <row r="107" ht="15">
-      <c r="A107" s="28"/>
+      <c r="A107" s="30"/>
       <c r="D107" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J107" s="28"/>
+      <c r="J107" s="30"/>
     </row>
     <row r="108" ht="15">
-      <c r="A108" s="28"/>
+      <c r="A108" s="30"/>
       <c r="D108" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J108" s="28"/>
+      <c r="J108" s="30"/>
     </row>
     <row r="109" ht="15">
-      <c r="A109" s="28"/>
+      <c r="A109" s="30"/>
       <c r="D109" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J109" s="28"/>
+      <c r="J109" s="30"/>
     </row>
     <row r="110" ht="15">
-      <c r="A110" s="28"/>
+      <c r="A110" s="30"/>
       <c r="D110" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J110" s="28"/>
+      <c r="J110" s="30"/>
     </row>
     <row r="111" ht="15">
-      <c r="A111" s="28"/>
+      <c r="A111" s="30"/>
       <c r="D111" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J111" s="28"/>
+      <c r="J111" s="30"/>
     </row>
     <row r="112" ht="15">
-      <c r="A112" s="28"/>
+      <c r="A112" s="30"/>
       <c r="D112" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J112" s="28"/>
+      <c r="J112" s="30"/>
     </row>
     <row r="113" ht="15">
-      <c r="A113" s="28"/>
+      <c r="A113" s="30"/>
       <c r="D113" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J113" s="28"/>
+      <c r="J113" s="30"/>
     </row>
     <row r="114" ht="15">
-      <c r="A114" s="28"/>
+      <c r="A114" s="30"/>
       <c r="D114" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J114" s="28"/>
+      <c r="J114" s="30"/>
     </row>
     <row r="115" ht="15">
-      <c r="A115" s="28"/>
+      <c r="A115" s="30"/>
       <c r="D115" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J115" s="28"/>
+      <c r="J115" s="30"/>
     </row>
     <row r="116" ht="15">
-      <c r="A116" s="28"/>
+      <c r="A116" s="30"/>
       <c r="D116" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J116" s="28"/>
+      <c r="J116" s="30"/>
     </row>
     <row r="117" ht="15">
-      <c r="A117" s="28"/>
+      <c r="A117" s="30"/>
       <c r="D117" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J117" s="28"/>
+      <c r="J117" s="30"/>
     </row>
     <row r="118" ht="15">
-      <c r="A118" s="28"/>
+      <c r="A118" s="30"/>
       <c r="D118" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J118" s="28"/>
+      <c r="J118" s="30"/>
     </row>
     <row r="119" ht="15">
-      <c r="A119" s="28"/>
+      <c r="A119" s="30"/>
       <c r="D119" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J119" s="28"/>
+      <c r="J119" s="30"/>
     </row>
     <row r="120" ht="15">
-      <c r="A120" s="28"/>
+      <c r="A120" s="30"/>
       <c r="D120" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J120" s="28"/>
+      <c r="J120" s="30"/>
     </row>
     <row r="121" ht="15">
-      <c r="A121" s="28"/>
+      <c r="A121" s="30"/>
       <c r="D121" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J121" s="28"/>
+      <c r="J121" s="30"/>
     </row>
     <row r="122" ht="15">
-      <c r="A122" s="28"/>
+      <c r="A122" s="30"/>
       <c r="D122" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J122" s="28"/>
+      <c r="J122" s="30"/>
     </row>
     <row r="123" ht="15">
-      <c r="A123" s="28"/>
+      <c r="A123" s="30"/>
       <c r="D123" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J123" s="28"/>
+      <c r="J123" s="30"/>
     </row>
     <row r="124" ht="15">
-      <c r="A124" s="28"/>
+      <c r="A124" s="30"/>
       <c r="D124" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J124" s="28"/>
+      <c r="J124" s="30"/>
     </row>
     <row r="125" ht="15">
-      <c r="A125" s="28"/>
+      <c r="A125" s="30"/>
       <c r="D125" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J125" s="28"/>
+      <c r="J125" s="30"/>
     </row>
     <row r="126" ht="15">
-      <c r="A126" s="28"/>
+      <c r="A126" s="30"/>
       <c r="D126" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J126" s="28"/>
+      <c r="J126" s="30"/>
     </row>
     <row r="127" ht="15">
-      <c r="A127" s="28"/>
+      <c r="A127" s="30"/>
       <c r="D127" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J127" s="28"/>
+      <c r="J127" s="30"/>
     </row>
     <row r="128" ht="15">
-      <c r="A128" s="28"/>
+      <c r="A128" s="30"/>
       <c r="D128" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J128" s="28"/>
+      <c r="J128" s="30"/>
     </row>
     <row r="129" ht="15">
-      <c r="A129" s="28"/>
+      <c r="A129" s="30"/>
       <c r="D129" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J129" s="28"/>
+      <c r="J129" s="30"/>
     </row>
     <row r="130" ht="15">
-      <c r="A130" s="28"/>
+      <c r="A130" s="30"/>
       <c r="D130" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J130" s="28"/>
+      <c r="J130" s="30"/>
     </row>
     <row r="131" ht="15">
-      <c r="A131" s="28"/>
+      <c r="A131" s="30"/>
       <c r="D131" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J131" s="28"/>
+      <c r="J131" s="30"/>
     </row>
     <row r="132" ht="15">
-      <c r="A132" s="28"/>
+      <c r="A132" s="30"/>
       <c r="D132" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J132" s="28"/>
+      <c r="J132" s="30"/>
     </row>
     <row r="133" ht="15">
-      <c r="A133" s="28"/>
+      <c r="A133" s="30"/>
       <c r="D133" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J133" s="28"/>
+      <c r="J133" s="30"/>
     </row>
     <row r="134" ht="15">
-      <c r="A134" s="28"/>
+      <c r="A134" s="30"/>
       <c r="D134" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J134" s="28"/>
+      <c r="J134" s="30"/>
     </row>
     <row r="135" ht="15">
-      <c r="A135" s="28"/>
+      <c r="A135" s="30"/>
       <c r="D135" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J135" s="28"/>
+      <c r="J135" s="30"/>
     </row>
     <row r="136" ht="15">
-      <c r="A136" s="28"/>
+      <c r="A136" s="30"/>
       <c r="D136" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J136" s="28"/>
+      <c r="J136" s="30"/>
     </row>
     <row r="137" ht="15">
-      <c r="A137" s="28"/>
+      <c r="A137" s="30"/>
       <c r="D137" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J137" s="28"/>
+      <c r="J137" s="30"/>
     </row>
     <row r="138" ht="15">
-      <c r="A138" s="28"/>
+      <c r="A138" s="30"/>
       <c r="D138" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J138" s="28"/>
+      <c r="J138" s="30"/>
     </row>
     <row r="139" ht="15">
-      <c r="A139" s="28"/>
+      <c r="A139" s="30"/>
       <c r="D139" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J139" s="28"/>
+      <c r="J139" s="30"/>
     </row>
     <row r="140" ht="15">
-      <c r="A140" s="28"/>
+      <c r="A140" s="30"/>
       <c r="D140" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J140" s="28"/>
+      <c r="J140" s="30"/>
     </row>
     <row r="141" ht="15">
-      <c r="A141" s="28"/>
+      <c r="A141" s="30"/>
       <c r="D141" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J141" s="28"/>
+      <c r="J141" s="30"/>
     </row>
     <row r="142" ht="15">
-      <c r="A142" s="28"/>
+      <c r="A142" s="30"/>
       <c r="D142" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J142" s="28"/>
+      <c r="J142" s="30"/>
     </row>
     <row r="143" ht="15">
-      <c r="A143" s="28"/>
+      <c r="A143" s="30"/>
       <c r="D143" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J143" s="28"/>
+      <c r="J143" s="30"/>
     </row>
     <row r="144" ht="15">
-      <c r="A144" s="28"/>
+      <c r="A144" s="30"/>
       <c r="D144" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J144" s="28"/>
+      <c r="J144" s="30"/>
     </row>
     <row r="145" ht="15">
-      <c r="A145" s="28"/>
+      <c r="A145" s="30"/>
       <c r="D145" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J145" s="28"/>
+      <c r="J145" s="30"/>
     </row>
     <row r="146" ht="15">
-      <c r="A146" s="28"/>
+      <c r="A146" s="30"/>
       <c r="D146" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J146" s="28"/>
+      <c r="J146" s="30"/>
     </row>
     <row r="147" ht="15">
-      <c r="A147" s="28"/>
+      <c r="A147" s="30"/>
       <c r="D147" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J147" s="28"/>
+      <c r="J147" s="30"/>
     </row>
     <row r="148" ht="15">
-      <c r="A148" s="28"/>
+      <c r="A148" s="30"/>
       <c r="D148" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J148" s="28"/>
+      <c r="J148" s="30"/>
     </row>
     <row r="149" ht="15">
-      <c r="A149" s="28"/>
+      <c r="A149" s="30"/>
       <c r="D149" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J149" s="28"/>
+      <c r="J149" s="30"/>
     </row>
     <row r="150" ht="15">
-      <c r="A150" s="28"/>
+      <c r="A150" s="30"/>
       <c r="D150" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J150" s="28"/>
+      <c r="J150" s="30"/>
     </row>
     <row r="151" ht="15">
-      <c r="A151" s="28"/>
+      <c r="A151" s="30"/>
       <c r="D151" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J151" s="28"/>
+      <c r="J151" s="30"/>
     </row>
     <row r="152" ht="15">
-      <c r="A152" s="28"/>
+      <c r="A152" s="30"/>
       <c r="D152" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J152" s="28"/>
+      <c r="J152" s="30"/>
     </row>
     <row r="153" ht="15">
-      <c r="A153" s="28"/>
+      <c r="A153" s="30"/>
       <c r="D153" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J153" s="28"/>
+      <c r="J153" s="30"/>
     </row>
     <row r="154" ht="15">
-      <c r="A154" s="28"/>
+      <c r="A154" s="30"/>
       <c r="D154" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J154" s="28"/>
+      <c r="J154" s="30"/>
     </row>
     <row r="155" ht="15">
-      <c r="A155" s="28"/>
+      <c r="A155" s="30"/>
       <c r="D155" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J155" s="28"/>
+      <c r="J155" s="30"/>
     </row>
     <row r="156" ht="15">
-      <c r="A156" s="28"/>
+      <c r="A156" s="30"/>
       <c r="D156" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J156" s="28"/>
+      <c r="J156" s="30"/>
     </row>
     <row r="157" ht="15">
-      <c r="A157" s="28"/>
+      <c r="A157" s="30"/>
       <c r="D157" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J157" s="28"/>
+      <c r="J157" s="30"/>
     </row>
     <row r="158" ht="15">
-      <c r="A158" s="28"/>
+      <c r="A158" s="30"/>
       <c r="D158" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J158" s="28"/>
+      <c r="J158" s="30"/>
     </row>
     <row r="159" ht="15">
-      <c r="A159" s="28"/>
+      <c r="A159" s="30"/>
       <c r="D159" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J159" s="28"/>
+      <c r="J159" s="30"/>
     </row>
     <row r="160" ht="15">
-      <c r="A160" s="28"/>
+      <c r="A160" s="30"/>
       <c r="D160" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J160" s="28"/>
+      <c r="J160" s="30"/>
     </row>
     <row r="161" ht="15">
-      <c r="A161" s="28"/>
+      <c r="A161" s="30"/>
       <c r="D161" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J161" s="28"/>
+      <c r="J161" s="30"/>
     </row>
     <row r="162" ht="15">
-      <c r="A162" s="28"/>
+      <c r="A162" s="30"/>
       <c r="D162" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J162" s="28"/>
+      <c r="J162" s="30"/>
     </row>
     <row r="163" ht="15">
-      <c r="A163" s="28"/>
+      <c r="A163" s="30"/>
       <c r="D163" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J163" s="28"/>
+      <c r="J163" s="30"/>
     </row>
     <row r="164" ht="15">
-      <c r="A164" s="28"/>
+      <c r="A164" s="30"/>
       <c r="D164" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J164" s="28"/>
+      <c r="J164" s="30"/>
     </row>
     <row r="165" ht="15">
-      <c r="A165" s="28"/>
+      <c r="A165" s="30"/>
       <c r="D165" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J165" s="28"/>
+      <c r="J165" s="30"/>
     </row>
     <row r="166" ht="15">
-      <c r="A166" s="28"/>
+      <c r="A166" s="30"/>
       <c r="D166" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J166" s="28"/>
+      <c r="J166" s="30"/>
     </row>
     <row r="167" ht="15">
-      <c r="A167" s="28"/>
+      <c r="A167" s="30"/>
       <c r="D167" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J167" s="28"/>
+      <c r="J167" s="30"/>
     </row>
     <row r="168" ht="15">
-      <c r="A168" s="28"/>
+      <c r="A168" s="30"/>
       <c r="D168" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J168" s="28"/>
+      <c r="J168" s="30"/>
     </row>
     <row r="169" ht="15">
-      <c r="A169" s="28"/>
+      <c r="A169" s="30"/>
       <c r="D169" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J169" s="28"/>
+      <c r="J169" s="30"/>
     </row>
     <row r="170" ht="15">
-      <c r="A170" s="28"/>
+      <c r="A170" s="30"/>
       <c r="D170" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J170" s="28"/>
+      <c r="J170" s="30"/>
     </row>
     <row r="171" ht="15">
-      <c r="A171" s="28"/>
+      <c r="A171" s="30"/>
       <c r="D171" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J171" s="28"/>
+      <c r="J171" s="30"/>
     </row>
     <row r="172" ht="15">
-      <c r="A172" s="28"/>
+      <c r="A172" s="30"/>
       <c r="D172" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J172" s="28"/>
+      <c r="J172" s="30"/>
     </row>
     <row r="173" ht="15">
-      <c r="A173" s="28"/>
+      <c r="A173" s="30"/>
       <c r="D173" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J173" s="28"/>
+      <c r="J173" s="30"/>
     </row>
     <row r="174" ht="15">
-      <c r="A174" s="28"/>
+      <c r="A174" s="30"/>
       <c r="D174" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J174" s="28"/>
+      <c r="J174" s="30"/>
     </row>
     <row r="175" ht="15">
-      <c r="A175" s="28"/>
+      <c r="A175" s="30"/>
       <c r="D175" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J175" s="28"/>
+      <c r="J175" s="30"/>
     </row>
     <row r="176" ht="15">
-      <c r="A176" s="28"/>
+      <c r="A176" s="30"/>
       <c r="D176" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J176" s="28"/>
+      <c r="J176" s="30"/>
     </row>
     <row r="177" ht="15">
-      <c r="A177" s="28"/>
+      <c r="A177" s="30"/>
       <c r="D177" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J177" s="28"/>
+      <c r="J177" s="30"/>
     </row>
     <row r="178" ht="15">
-      <c r="A178" s="28"/>
+      <c r="A178" s="30"/>
       <c r="D178" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J178" s="28"/>
+      <c r="J178" s="30"/>
     </row>
     <row r="179" ht="15">
-      <c r="A179" s="28"/>
+      <c r="A179" s="30"/>
       <c r="D179" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J179" s="28"/>
+      <c r="J179" s="30"/>
     </row>
     <row r="180" ht="15">
-      <c r="A180" s="28"/>
+      <c r="A180" s="30"/>
       <c r="D180" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J180" s="28"/>
+      <c r="J180" s="30"/>
     </row>
     <row r="181" ht="15">
-      <c r="A181" s="28"/>
+      <c r="A181" s="30"/>
       <c r="D181" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J181" s="28"/>
+      <c r="J181" s="30"/>
     </row>
     <row r="182" ht="15">
-      <c r="A182" s="28"/>
+      <c r="A182" s="30"/>
       <c r="D182" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J182" s="28"/>
+      <c r="J182" s="30"/>
     </row>
     <row r="183" ht="15">
-      <c r="A183" s="28"/>
+      <c r="A183" s="30"/>
       <c r="D183" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J183" s="28"/>
+      <c r="J183" s="30"/>
     </row>
     <row r="184" ht="15">
-      <c r="A184" s="28"/>
+      <c r="A184" s="30"/>
       <c r="D184" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J184" s="28"/>
+      <c r="J184" s="30"/>
     </row>
     <row r="185" ht="15">
-      <c r="A185" s="28"/>
+      <c r="A185" s="30"/>
       <c r="D185" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J185" s="28"/>
+      <c r="J185" s="30"/>
     </row>
     <row r="186" ht="15">
-      <c r="A186" s="28"/>
+      <c r="A186" s="30"/>
       <c r="D186" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J186" s="28"/>
+      <c r="J186" s="30"/>
     </row>
     <row r="187" ht="15">
-      <c r="A187" s="28"/>
+      <c r="A187" s="30"/>
       <c r="D187" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J187" s="28"/>
+      <c r="J187" s="30"/>
     </row>
     <row r="188" ht="15">
-      <c r="A188" s="28"/>
+      <c r="A188" s="30"/>
       <c r="D188" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J188" s="28"/>
+      <c r="J188" s="30"/>
     </row>
     <row r="189" ht="15">
-      <c r="A189" s="28"/>
+      <c r="A189" s="30"/>
       <c r="D189" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J189" s="28"/>
+      <c r="J189" s="30"/>
     </row>
     <row r="190" ht="15">
-      <c r="A190" s="28"/>
+      <c r="A190" s="30"/>
       <c r="D190" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J190" s="28"/>
+      <c r="J190" s="30"/>
     </row>
     <row r="191" ht="15">
-      <c r="A191" s="28"/>
+      <c r="A191" s="30"/>
       <c r="D191" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J191" s="28"/>
+      <c r="J191" s="30"/>
     </row>
     <row r="192" ht="15">
-      <c r="A192" s="28"/>
+      <c r="A192" s="30"/>
       <c r="D192" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J192" s="28"/>
+      <c r="J192" s="30"/>
     </row>
     <row r="193" ht="15">
-      <c r="A193" s="28"/>
+      <c r="A193" s="30"/>
       <c r="D193" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J193" s="28"/>
+      <c r="J193" s="30"/>
     </row>
     <row r="194" ht="15">
-      <c r="A194" s="28"/>
+      <c r="A194" s="30"/>
       <c r="D194" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J194" s="28"/>
+      <c r="J194" s="30"/>
     </row>
     <row r="195" ht="15">
-      <c r="A195" s="28"/>
+      <c r="A195" s="30"/>
       <c r="D195" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J195" s="28"/>
+      <c r="J195" s="30"/>
     </row>
     <row r="196" ht="15">
-      <c r="A196" s="28"/>
+      <c r="A196" s="30"/>
       <c r="D196" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J196" s="28"/>
+      <c r="J196" s="30"/>
     </row>
     <row r="197" ht="15">
-      <c r="A197" s="28"/>
+      <c r="A197" s="30"/>
       <c r="D197" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J197" s="28"/>
+      <c r="J197" s="30"/>
     </row>
     <row r="198" ht="15">
-      <c r="A198" s="28"/>
+      <c r="A198" s="30"/>
       <c r="D198" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J198" s="28"/>
+      <c r="J198" s="30"/>
     </row>
     <row r="199" ht="15">
-      <c r="A199" s="28"/>
+      <c r="A199" s="30"/>
       <c r="D199" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J199" s="28"/>
+      <c r="J199" s="30"/>
     </row>
     <row r="200" ht="15">
-      <c r="A200" s="28"/>
+      <c r="A200" s="30"/>
       <c r="D200" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J200" s="28"/>
+      <c r="J200" s="30"/>
     </row>
     <row r="201" ht="15">
-      <c r="A201" s="28"/>
+      <c r="A201" s="30"/>
       <c r="D201" s="1" t="s">
         <v>481</v>
       </c>
-      <c r="J201" s="28"/>
+      <c r="J201" s="30"/>
     </row>
   </sheetData>
   <printOptions headings="0" gridLines="0" horizontalCentered="0" verticalCentered="0"/>
@@ -11016,7 +11024,7 @@
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
       <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="2" disablePrompts="0">
-        <x14:dataValidation xr:uid="{F5A6C0CF-EF64-4011-B35E-E0B3B77D0133}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{8F50AE33-0C82-4CBF-B975-842049930CDC}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Build,Troubleshoot,Rebuild,Timed Mock,Review"</xm:f>
           </x14:formula1>
@@ -11025,7 +11033,7 @@
           </x14:formula2>
           <xm:sqref>D2:D201</xm:sqref>
         </x14:dataValidation>
-        <x14:dataValidation xr:uid="{621BD406-F3F6-4FCF-BECB-8C0F543E05DD}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
+        <x14:dataValidation xr:uid="{495835BB-0F15-4EA4-86D9-3DD92D8EF565}" type="list" allowBlank="0" errorStyle="stop" imeMode="noControl" operator="between" showDropDown="0" showErrorMessage="0" showInputMessage="0">
           <x14:formula1>
             <xm:f>"Pass,Partial,Fail"</xm:f>
           </x14:formula1>
@@ -11054,211 +11062,211 @@
   </cols>
   <sheetData>
     <row r="1" ht="34" customHeight="1">
-      <c r="A1" s="26" t="s">
+      <c r="A1" s="28" t="s">
         <v>482</v>
       </c>
-      <c r="B1" s="26"/>
-      <c r="C1" s="26"/>
-      <c r="D1" s="26"/>
-      <c r="E1" s="26"/>
-      <c r="F1" s="26"/>
+      <c r="B1" s="28"/>
+      <c r="C1" s="28"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
     </row>
     <row r="3" ht="15">
-      <c r="A3" s="27" t="s">
+      <c r="A3" s="29" t="s">
         <v>483</v>
       </c>
-      <c r="B3" s="27" t="s">
+      <c r="B3" s="29" t="s">
         <v>484</v>
       </c>
-      <c r="C3" s="27" t="s">
+      <c r="C3" s="29" t="s">
         <v>485</v>
       </c>
     </row>
     <row r="4" ht="15">
-      <c r="A4" s="27" t="s">
+      <c r="A4" s="29" t="s">
         <v>486</v>
       </c>
-      <c r="B4" s="27" t="s">
+      <c r="B4" s="29" t="s">
         <v>487</v>
       </c>
-      <c r="C4" s="27" t="s">
+      <c r="C4" s="29" t="s">
         <v>488</v>
       </c>
     </row>
     <row r="5" ht="15">
-      <c r="A5" s="27" t="s">
+      <c r="A5" s="29" t="s">
         <v>489</v>
       </c>
-      <c r="B5" s="27" t="s">
-        <v>481</v>
-      </c>
-      <c r="C5" s="27" t="s">
+      <c r="B5" s="29" t="s">
+        <v>481</v>
+      </c>
+      <c r="C5" s="29" t="s">
         <v>490</v>
       </c>
     </row>
     <row r="6" ht="15">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="29" t="s">
         <v>491</v>
       </c>
-      <c r="B6" s="27" t="s">
+      <c r="B6" s="29" t="s">
         <v>492</v>
       </c>
-      <c r="C6" s="27" t="s">
+      <c r="C6" s="29" t="s">
         <v>493</v>
       </c>
     </row>
     <row r="7" ht="15">
-      <c r="A7" s="27" t="s">
+      <c r="A7" s="29" t="s">
         <v>494</v>
       </c>
-      <c r="B7" s="27" t="s">
+      <c r="B7" s="29" t="s">
         <v>495</v>
       </c>
-      <c r="C7" s="27" t="s">
+      <c r="C7" s="29" t="s">
         <v>496</v>
       </c>
     </row>
     <row r="8" ht="15">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="29" t="s">
         <v>497</v>
       </c>
-      <c r="B8" s="27" t="s">
+      <c r="B8" s="29" t="s">
         <v>498</v>
       </c>
-      <c r="C8" s="27" t="s">
+      <c r="C8" s="29" t="s">
         <v>499</v>
       </c>
     </row>
     <row r="9" ht="15">
-      <c r="A9" s="27" t="s">
+      <c r="A9" s="29" t="s">
         <v>500</v>
       </c>
-      <c r="B9" s="27" t="s">
+      <c r="B9" s="29" t="s">
         <v>501</v>
       </c>
-      <c r="C9" s="27" t="s">
+      <c r="C9" s="29" t="s">
         <v>502</v>
       </c>
     </row>
     <row r="10" ht="15">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="29" t="s">
         <v>503</v>
       </c>
-      <c r="B10" s="27" t="s">
+      <c r="B10" s="29" t="s">
         <v>504</v>
       </c>
-      <c r="C10" s="27" t="s">
+      <c r="C10" s="29" t="s">
         <v>505</v>
       </c>
     </row>
     <row r="11" ht="15">
-      <c r="A11" s="27" t="s">
+      <c r="A11" s="29" t="s">
         <v>506</v>
       </c>
-      <c r="B11" s="27" t="s">
+      <c r="B11" s="29" t="s">
         <v>507</v>
       </c>
-      <c r="C11" s="27" t="s">
+      <c r="C11" s="29" t="s">
         <v>508</v>
       </c>
     </row>
     <row r="12" ht="15">
-      <c r="A12" s="27" t="s">
+      <c r="A12" s="29" t="s">
         <v>509</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="29" t="s">
         <v>510</v>
       </c>
-      <c r="C12" s="27" t="s">
+      <c r="C12" s="29" t="s">
         <v>511</v>
       </c>
     </row>
     <row r="13" ht="15">
-      <c r="A13" s="27" t="s">
+      <c r="A13" s="29" t="s">
         <v>512</v>
       </c>
-      <c r="B13" s="27" t="s">
+      <c r="B13" s="29" t="s">
         <v>513</v>
       </c>
-      <c r="C13" s="27" t="s">
+      <c r="C13" s="29" t="s">
         <v>514</v>
       </c>
     </row>
     <row r="15" ht="15">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="33" t="s">
         <v>515</v>
       </c>
-      <c r="B15" s="31"/>
-      <c r="C15" s="31"/>
-      <c r="D15" s="31"/>
-      <c r="E15" s="31"/>
-      <c r="F15" s="31"/>
+      <c r="B15" s="33"/>
+      <c r="C15" s="33"/>
+      <c r="D15" s="33"/>
+      <c r="E15" s="33"/>
+      <c r="F15" s="33"/>
     </row>
     <row r="17" ht="15">
-      <c r="A17" s="27" t="s">
+      <c r="A17" s="29" t="s">
         <v>516</v>
       </c>
-      <c r="B17" s="27" t="s">
+      <c r="B17" s="29" t="s">
         <v>517</v>
       </c>
     </row>
     <row r="18" ht="23.850000000000001">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="29" t="s">
         <v>518</v>
       </c>
-      <c r="B18" s="27" t="s">
+      <c r="B18" s="29" t="s">
         <v>519</v>
       </c>
     </row>
     <row r="19" ht="23.850000000000001">
-      <c r="A19" s="27" t="s">
+      <c r="A19" s="29" t="s">
         <v>520</v>
       </c>
-      <c r="B19" s="27" t="s">
+      <c r="B19" s="29" t="s">
         <v>521</v>
       </c>
     </row>
     <row r="20" ht="23.850000000000001">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="29" t="s">
         <v>522</v>
       </c>
-      <c r="B20" s="27" t="s">
+      <c r="B20" s="29" t="s">
         <v>523</v>
       </c>
     </row>
     <row r="21" ht="15">
-      <c r="A21" s="27" t="s">
+      <c r="A21" s="29" t="s">
         <v>372</v>
       </c>
-      <c r="B21" s="27" t="s">
+      <c r="B21" s="29" t="s">
         <v>524</v>
       </c>
     </row>
     <row r="22" ht="15">
-      <c r="A22" s="27" t="s">
+      <c r="A22" s="29" t="s">
         <v>525</v>
       </c>
-      <c r="B22" s="27" t="s">
+      <c r="B22" s="29" t="s">
         <v>526</v>
       </c>
     </row>
     <row r="23" ht="15">
-      <c r="A23" s="27" t="s">
+      <c r="A23" s="29" t="s">
         <v>527</v>
       </c>
-      <c r="B23" s="27" t="s">
+      <c r="B23" s="29" t="s">
         <v>528</v>
       </c>
     </row>
     <row r="25" ht="15" customHeight="1">
-      <c r="A25" s="32" t="s">
+      <c r="A25" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="B25" s="32"/>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
+      <c r="B25" s="34"/>
+      <c r="C25" s="34"/>
+      <c r="D25" s="34"/>
+      <c r="E25" s="34"/>
+      <c r="F25" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -11304,7 +11312,7 @@
     </row>
     <row r="2" ht="15">
       <c r="A2" s="1" t="s">
-        <v>60</v>
+        <v>63</v>
       </c>
       <c r="B2" s="1">
         <v>0</v>
